--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -431,7 +431,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11144250"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10534650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 01:39</t>
+          <t>2026-07-18 10:29</t>
         </is>
       </c>
     </row>
@@ -1276,55 +1276,51 @@
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.798</v>
+        <v>4.8</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>5.433</v>
+        <v>5.467</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>5.067</v>
+        <v>4.8</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H71" s="35" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+      <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="35" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>4.667</v>
+        <v>4.6</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>4.4</v>
+        <v>4.333</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.714</v>
+        <v>4.718</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
@@ -1576,32 +1572,32 @@
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>0.679</v>
+        <v>0.671</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="E75" s="32" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="F75" s="32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>21st</t>
+      <c r="H75" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr"/>
       <c r="J75" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="K75" s="32" t="n">
@@ -1617,10 +1613,10 @@
         <v>0.15</v>
       </c>
       <c r="O75" s="32" t="n">
-        <v>0.167</v>
+        <v>0.1</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
@@ -1729,55 +1725,51 @@
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>5.179</v>
+        <v>5.141</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>6.033</v>
+        <v>6</v>
       </c>
       <c r="D79" s="32" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="E79" s="32" t="n">
         <v>5.667</v>
       </c>
       <c r="F79" s="32" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="G79" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>16th</t>
+          <t>13th</t>
         </is>
       </c>
       <c r="K79" s="32" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="L79" s="32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M79" s="32" t="n">
-        <v>4.067</v>
+        <v>3.667</v>
       </c>
       <c r="N79" s="32" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>5.033</v>
+        <v>4.767</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.94</v>
+        <v>4.906</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
@@ -2029,51 +2021,51 @@
         </is>
       </c>
       <c r="B83" s="32" t="n">
-        <v>0.458</v>
+        <v>0.464</v>
       </c>
       <c r="C83" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="D83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.533</v>
-      </c>
       <c r="F83" s="32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G83" s="32" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="35" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>11th</t>
         </is>
       </c>
       <c r="I83" s="32" t="inlineStr"/>
       <c r="J83" s="33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="K83" s="32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L83" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="M83" s="32" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="N83" s="32" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O83" s="32" t="n">
         <v>0.367</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>0.548</v>
+        <v>0.553</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
         <is>
@@ -2094,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,171 +2103,329 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Chicago White Sox offense vs Toronto Blue Jays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Chicago White Sox offense vs Toronto Blue Jays defense</t>
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>4.953</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.571</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>7.894</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.869</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>4.733</v>
+        <v>1.354</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>4.482</v>
+        <v>0.979</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>7.792</v>
+        <v>9.208</v>
       </c>
       <c r="C74" s="32" t="inlineStr">
         <is>
@@ -2339,396 +2489,396 @@
         </is>
       </c>
       <c r="P74" s="32" t="n">
-        <v>7.894</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>1.354</v>
-      </c>
-      <c r="C75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.627</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>0.767</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>0.979</v>
+        <v>0.554</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>9.208</v>
-      </c>
-      <c r="C76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>9.489000000000001</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays offense vs Chicago White Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B78" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F78" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G78" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H78" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I78" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J78" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K78" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L78" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M78" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N78" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O78" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P78" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q78" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>4.083</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays offense vs Chicago White Sox defense</t>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>4.553</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B80" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C80" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D80" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E80" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F80" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G80" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H80" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I80" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J80" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K80" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L80" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M80" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N80" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O80" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P80" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q80" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.854</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>4.084</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H81" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
+        <v>0.915</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>3.9</v>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>4.56</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.468</v>
+        <v>7.298</v>
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
@@ -2792,230 +2942,72 @@
         </is>
       </c>
       <c r="P82" s="32" t="n">
-        <v>7.854</v>
+        <v>7.938</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B83" s="32" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="C83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O83" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.458</v>
+      </c>
+      <c r="C83" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E83" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F83" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G83" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J83" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K83" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L83" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M83" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N83" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O83" s="32" t="n">
+        <v>0.5</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>1.062</v>
+        <v>0.53</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B84" s="32" t="n">
-        <v>7.298</v>
-      </c>
-      <c r="C84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I84" s="32" t="inlineStr"/>
-      <c r="J84" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P84" s="32" t="n">
-        <v>7.938</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B85" s="32" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="C85" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D85" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E85" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F85" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G85" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H85" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I85" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J85" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K85" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L85" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M85" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N85" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O85" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P85" s="32" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="Q85" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3152,55 +3144,51 @@
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>3.976</v>
+        <v>4.012</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>3.933</v>
+        <v>4</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>3.867</v>
+        <v>3.733</v>
       </c>
       <c r="F70" s="32" t="n">
         <v>3.8</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="H70" s="35" t="inlineStr">
         <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>5.467</v>
+        <v>5.733</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>5.45</v>
+        <v>5.7</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>5.567</v>
+        <v>5.5</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.575</v>
+        <v>5.591</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
@@ -3452,13 +3440,13 @@
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.512</v>
+        <v>0.518</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.433</v>
+        <v>0.467</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="E74" s="32" t="n">
         <v>0.333</v>
@@ -3467,36 +3455,40 @@
         <v>0.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>0.2</v>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L74" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N74" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="M74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.85</v>
-      </c>
       <c r="O74" s="32" t="n">
-        <v>0.867</v>
+        <v>0.9</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>0.721</v>
+        <v>0.724</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
@@ -3605,51 +3597,51 @@
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.793</v>
+        <v>4.761</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5.733</v>
+        <v>5.7</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="E78" s="32" t="n">
         <v>5.4</v>
       </c>
       <c r="F78" s="32" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="H78" s="36" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>30th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="L78" s="32" t="n">
         <v>3.8</v>
       </c>
       <c r="M78" s="32" t="n">
-        <v>4.667</v>
+        <v>4.333</v>
       </c>
       <c r="N78" s="32" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.1</v>
+        <v>4.067</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.627</v>
+        <v>4.595</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
@@ -3901,7 +3893,7 @@
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>0.523</v>
+        <v>0.517</v>
       </c>
       <c r="C82" s="32" t="n">
         <v>0.5669999999999999</v>
@@ -3910,23 +3902,23 @@
         <v>0.7</v>
       </c>
       <c r="E82" s="32" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="F82" s="32" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="H82" s="36" t="inlineStr">
         <is>
-          <t>23rd</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
       <c r="J82" s="35" t="inlineStr">
         <is>
-          <t>17th</t>
+          <t>18th</t>
         </is>
       </c>
       <c r="K82" s="32" t="n">
@@ -3945,7 +3937,7 @@
         <v>0.4</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>0.537</v>
+        <v>0.53</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
@@ -4107,9 +4099,9 @@
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
@@ -4399,7 +4391,7 @@
       </c>
       <c r="H75" s="35" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>21st</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr"/>
@@ -4552,13 +4544,13 @@
       </c>
       <c r="H79" s="36" t="inlineStr">
         <is>
-          <t>28th</t>
+          <t>29th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
       <c r="J79" s="35" t="inlineStr">
         <is>
-          <t>11th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="K79" s="32" t="n">
@@ -4854,7 +4846,7 @@
       <c r="I83" s="32" t="inlineStr"/>
       <c r="J83" s="36" t="inlineStr">
         <is>
-          <t>23rd</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="K83" s="32" t="n">
@@ -5012,10 +5004,10 @@
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.612</v>
+        <v>4.593</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>4.5</v>
+        <v>4.433</v>
       </c>
       <c r="D71" s="32" t="n">
         <v>4.65</v>
@@ -5024,14 +5016,14 @@
         <v>4.333</v>
       </c>
       <c r="F71" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="G71" s="32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr">
@@ -5041,26 +5033,26 @@
       </c>
       <c r="J71" s="36" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
         <v>5.4</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>5.733</v>
+        <v>5.4</v>
       </c>
       <c r="N71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="P71" s="32" t="n">
         <v>5</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>5.023</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
@@ -5312,10 +5304,10 @@
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>0.488</v>
+        <v>0.482</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>0.6</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D75" s="32" t="n">
         <v>0.55</v>
@@ -5331,20 +5323,20 @@
       </c>
       <c r="H75" s="36" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr"/>
       <c r="J75" s="35" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>17th</t>
         </is>
       </c>
       <c r="K75" s="32" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="L75" s="32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M75" s="32" t="n">
         <v>0.667</v>
@@ -5353,10 +5345,10 @@
         <v>0.55</v>
       </c>
       <c r="O75" s="32" t="n">
-        <v>0.733</v>
+        <v>0.667</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>0.643</v>
+        <v>0.635</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
@@ -5465,55 +5457,51 @@
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.919</v>
+        <v>4.885</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>4.567</v>
+        <v>4.6</v>
       </c>
       <c r="D79" s="32" t="n">
         <v>4.75</v>
       </c>
       <c r="E79" s="32" t="n">
-        <v>5.133</v>
+        <v>5.267</v>
       </c>
       <c r="F79" s="32" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G79" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>4.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
         </is>
       </c>
       <c r="K79" s="32" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="L79" s="32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="M79" s="32" t="n">
-        <v>3.933</v>
+        <v>4</v>
       </c>
       <c r="N79" s="32" t="n">
         <v>3.75</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>4</v>
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.718</v>
+        <v>4.686</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
@@ -5765,51 +5753,51 @@
         </is>
       </c>
       <c r="B83" s="32" t="n">
-        <v>0.679</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="C83" s="32" t="n">
-        <v>0.667</v>
+        <v>0.7</v>
       </c>
       <c r="D83" s="32" t="n">
         <v>0.5</v>
       </c>
       <c r="E83" s="32" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="F83" s="32" t="n">
         <v>0.6</v>
       </c>
       <c r="G83" s="32" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H83" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>9th</t>
         </is>
       </c>
       <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
+      <c r="J83" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="K83" s="32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L83" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="M83" s="32" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="N83" s="32" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O83" s="32" t="n">
-        <v>0.633</v>
+        <v>0.667</v>
       </c>
       <c r="P83" s="32" t="n">
-        <v>0.452</v>
+        <v>0.459</v>
       </c>
       <c r="Q83" s="34" t="inlineStr">
         <is>
@@ -5830,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5847,171 +5835,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.333</v>
+        <v>7.087</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5.322</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.087</v>
+        <v>1.022</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6075,22 +6142,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.022</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -6154,317 +6221,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.417</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.208</v>
+        <v>0.788</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.422</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.286</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.253</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
+        <v>7.792</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.2</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.256</v>
+        <v>7.848</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6528,22 +6591,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.848</v>
+        <v>0.848</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -6607,147 +6670,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.848</v>
+        <v>8.304</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.518</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.304</v>
+        <v>0.488</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6766,7 +6750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6783,167 +6767,325 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Arizona Diamondbacks defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Arizona Diamondbacks defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.188000000000001</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.482</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>1.109</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.2</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.405</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.826</v>
+        <v>8.196</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -7007,400 +7149,400 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.188000000000001</v>
+        <v>7.146</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.109</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.614</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.25</v>
+        <v>0.671</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.146</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.598</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.447</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks offense vs St. Louis Cardinals defense</t>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.442</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.542</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.452</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.233</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.7</v>
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.447</v>
+        <v>1.043</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.542</v>
+        <v>7.354</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -7464,226 +7606,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>7.739</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.541</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.467</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.043</v>
+        <v>0.542</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>7.354</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7702,7 +7686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7719,246 +7703,167 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Boston Red Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.627</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>2.733</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>3.233</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>3.939</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.553</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>2.967</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.391</v>
+        <v>3.881</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -8022,22 +7927,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.217</v>
+        <v>8.391</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -8101,317 +8006,321 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.587</v>
+        <v>1.217</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
-        <v>0.506</v>
-      </c>
-      <c r="C74" s="32" t="n">
+      <c r="B75" s="32" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="M75" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Boston Red Sox offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.256</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.767</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.333</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.967</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>4.482</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.739</v>
+        <v>8.304</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -8475,22 +8384,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.444</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.239000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -8554,68 +8463,151 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.778</v>
+        <v>1.444</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="32" t="n">
+      <c r="B83" s="32" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C83" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="D83" s="32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E83" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="F83" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="F82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="G83" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J83" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K83" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L83" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M83" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N83" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O83" s="32" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P83" s="32" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8856,10 +8848,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6817</v>
+        <v>0.6797</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-214</v>
+        <v>-212</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>178</v>
@@ -8886,7 +8878,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 68.2% (fair -214). Your call.</t>
+          <t>Model 68.0% (fair -212). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8922,10 +8914,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6525000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-188</v>
+        <v>-193</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8952,7 +8944,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 65.9% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8988,10 +8980,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6502</v>
+        <v>0.6522</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-186</v>
+        <v>-188</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -9018,7 +9010,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 65.2% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9120,13 +9112,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.7389</v>
+        <v>0.7423</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-283</v>
+        <v>-288</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9150,7 +9142,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 73.9% (fair -283). Your call.</t>
+          <t>Model 74.2% (fair -288). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9192,7 +9184,7 @@
         <v>-137</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9258,7 +9250,7 @@
         <v>-171</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9318,13 +9310,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6278</v>
+        <v>0.6493</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-169</v>
+        <v>-185</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9348,7 +9340,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 64.9% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9365,12 +9357,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9380,17 +9372,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.625</v>
+        <v>0.6099</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-167</v>
+        <v>-156</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9414,7 +9406,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9431,12 +9423,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9446,17 +9438,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6151</v>
+        <v>0.6209</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-160</v>
+        <v>-164</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9480,7 +9472,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9512,17 +9504,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5623</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-128</v>
+        <v>-131</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9546,7 +9538,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9563,12 +9555,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9578,17 +9570,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 147</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5092</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-142</v>
+        <v>-104</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9612,7 +9604,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9629,12 +9621,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9644,17 +9636,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5193</v>
+        <v>0.5662</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-108</v>
+        <v>-131</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9678,7 +9670,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9695,32 +9687,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Under 13</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4219</v>
+        <v>0.5543</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>137</v>
+        <v>-124</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>165</v>
+        <v>106</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9744,7 +9736,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9761,12 +9753,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Toronto Blue Jays</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9776,17 +9768,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.416</v>
+        <v>0.4219</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9810,7 +9802,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9822,37 +9814,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4984</v>
+        <v>0.412</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9876,7 +9868,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9888,37 +9880,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5194</v>
+        <v>0.4967</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9942,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9959,12 +9951,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9974,17 +9966,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5234</v>
+        <v>0.5281</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10008,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10020,34 +10012,34 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Toronto Blue Jays</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5281</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-106</v>
+        <v>-112</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>104</v>
@@ -10074,7 +10066,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10091,32 +10083,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.4778</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-105</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10140,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10157,12 +10149,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10172,17 +10164,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.5234</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-105</v>
+        <v>102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10206,7 +10198,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10218,17 +10210,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10238,17 +10230,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5399</v>
+        <v>0.5377</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-107</v>
+        <v>-104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10272,7 +10264,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10284,17 +10276,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10304,17 +10296,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5313</v>
+        <v>0.5166999999999999</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10338,7 +10330,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10355,7 +10347,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -10365,22 +10357,22 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4517999999999999</v>
+        <v>0.5178</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>121</v>
+        <v>-107</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10404,7 +10396,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10421,32 +10413,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.612</v>
+        <v>0.4772</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-158</v>
+        <v>110</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-147</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10470,7 +10462,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10647,13 +10639,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.45495</v>
+        <v>0.4588</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10677,7 +10669,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10713,10 +10705,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.54505</v>
+        <v>0.5412</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-117</v>
@@ -10743,7 +10735,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10779,13 +10771,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.625</v>
+        <v>0.6209</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-167</v>
+        <v>-164</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10809,7 +10801,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10845,13 +10837,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.375</v>
+        <v>0.3791</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-104</v>
+        <v>125</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10875,7 +10867,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10911,10 +10903,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3475</v>
+        <v>0.3409</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>178</v>
@@ -10941,7 +10933,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 34.8% (fair +188). Your call.</t>
+          <t>Model 34.1% (fair +193). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10977,10 +10969,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6525000000000001</v>
+        <v>0.6591</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-188</v>
+        <v>-193</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -11007,7 +10999,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 65.9% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11043,13 +11035,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5124016</v>
+        <v>0.4772</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -11073,7 +11065,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -11109,10 +11101,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4875983999999999</v>
+        <v>0.5228</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>105</v>
+        <v>-110</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-117</v>
@@ -11139,7 +11131,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11175,13 +11167,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6278</v>
+        <v>0.6493</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-169</v>
+        <v>-185</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11205,7 +11197,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 64.9% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11241,13 +11233,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3722</v>
+        <v>0.3507</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>125</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11271,7 +11263,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11307,10 +11299,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3183</v>
+        <v>0.3203</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>178</v>
@@ -11337,7 +11329,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 31.8% (fair +214). Your call.</t>
+          <t>Model 32.0% (fair +212). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11373,10 +11365,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6817</v>
+        <v>0.6797</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-214</v>
+        <v>-212</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -11403,7 +11395,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 68.2% (fair -214). Your call.</t>
+          <t>Model 68.0% (fair -212). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11439,13 +11431,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4276</v>
+        <v>0.4316</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11469,7 +11461,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 43.2% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11505,13 +11497,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5724</v>
+        <v>0.5684</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-134</v>
+        <v>-132</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-133</v>
+        <v>-130</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11535,7 +11527,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 56.8% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11571,13 +11563,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5193</v>
+        <v>0.5092</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11601,7 +11593,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11637,13 +11629,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4807</v>
+        <v>0.4908</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11667,7 +11659,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11703,13 +11695,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3963</v>
+        <v>0.3961</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>152</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11769,13 +11761,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6037</v>
+        <v>0.6039</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-152</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11835,13 +11827,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5301</v>
+        <v>0.5166999999999999</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-113</v>
+        <v>-107</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-107</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11865,7 +11857,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11901,13 +11893,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4699</v>
+        <v>0.4833</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11931,7 +11923,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11963,17 +11955,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4845</v>
+        <v>0.4573</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11997,7 +11989,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12029,17 +12021,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.4555999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-106</v>
+        <v>119</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12063,7 +12055,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12099,13 +12091,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.584</v>
+        <v>0.588</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-140</v>
+        <v>-143</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-160</v>
+        <v>-167</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12129,7 +12121,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12165,13 +12157,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.416</v>
+        <v>0.412</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12195,7 +12187,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12363,13 +12355,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4418</v>
+        <v>0.3754</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-105</v>
+        <v>112</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12393,7 +12385,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 37.5% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12429,13 +12421,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4879</v>
+        <v>0.5543</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>105</v>
+        <v>-124</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12459,7 +12451,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12495,13 +12487,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.612</v>
+        <v>0.6072</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-158</v>
+        <v>-155</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-147</v>
+        <v>-144</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12525,7 +12517,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 60.7% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12561,13 +12553,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.388</v>
+        <v>0.3928</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -12591,7 +12583,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 39.3% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12633,7 +12625,7 @@
         <v>286</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12755,17 +12747,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4197</v>
+        <v>0.5222</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>138</v>
+        <v>-109</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>112</v>
+        <v>-108</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12789,7 +12781,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12821,17 +12813,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4937</v>
+        <v>0.4778</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12855,7 +12847,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12891,13 +12883,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.4466</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12921,7 +12913,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +128). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12957,13 +12949,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5534</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-128</v>
+        <v>-124</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12987,7 +12979,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -128). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13023,10 +13015,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4919</v>
+        <v>0.4898</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>100</v>
@@ -13053,7 +13045,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13089,13 +13081,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5081</v>
+        <v>0.5102</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13119,7 +13111,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13155,13 +13147,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.461</v>
+        <v>0.4607</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>117</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-102</v>
+        <v>104</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13221,13 +13213,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4517999999999999</v>
+        <v>0.4521</v>
       </c>
       <c r="G44" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13287,10 +13279,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.6099</v>
+        <v>0.611</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-167</v>
@@ -13317,7 +13309,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13353,10 +13345,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.3901</v>
+        <v>0.389</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>163</v>
@@ -13383,7 +13375,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13419,13 +13411,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.4822</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13449,7 +13441,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13485,13 +13477,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.5178</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13515,7 +13507,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13547,17 +13539,17 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 11</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4377</v>
+        <v>0.3577</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-108</v>
+        <v>103</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13581,7 +13573,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 35.8% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13613,17 +13605,17 @@
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5623</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-128</v>
+        <v>-131</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13647,7 +13639,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13683,13 +13675,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6052</v>
+        <v>0.6118</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-153</v>
+        <v>-158</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-147</v>
+        <v>-152</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13713,7 +13705,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13749,13 +13741,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3948</v>
+        <v>0.3882</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13779,7 +13771,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13815,13 +13807,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4657</v>
+        <v>0.4693000000000001</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13845,7 +13837,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13881,13 +13873,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5343</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13911,7 +13903,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13947,13 +13939,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3849</v>
+        <v>0.3901</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13977,7 +13969,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14013,13 +14005,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6151</v>
+        <v>0.6099</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14043,7 +14035,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14079,10 +14071,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3498</v>
+        <v>0.3478</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>178</v>
@@ -14109,7 +14101,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 34.8% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14145,10 +14137,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6502</v>
+        <v>0.6522</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-186</v>
+        <v>-188</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>178</v>
@@ -14175,7 +14167,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 65.2% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14211,13 +14203,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4601</v>
+        <v>0.4719</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14241,7 +14233,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14277,13 +14269,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5399</v>
+        <v>0.5281</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-117</v>
+        <v>-112</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-107</v>
+        <v>104</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14307,7 +14299,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14339,17 +14331,17 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4806</v>
+        <v>0.4355</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14373,7 +14365,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14405,17 +14397,17 @@
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5194</v>
+        <v>0.4776</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-108</v>
+        <v>109</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14439,7 +14431,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14481,7 +14473,7 @@
         <v>137</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -14547,7 +14539,7 @@
         <v>-137</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -14607,13 +14599,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4649</v>
+        <v>0.4673</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14637,7 +14629,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14673,13 +14665,13 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.5327</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-115</v>
+        <v>-114</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -14703,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14745,7 +14737,7 @@
         <v>171</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -14811,7 +14803,7 @@
         <v>-171</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -15003,10 +14995,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5094</v>
+        <v>0.5062</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15031,7 +15023,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.6% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15067,10 +15059,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4905</v>
+        <v>0.4938</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15095,7 +15087,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 49.4% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15259,13 +15251,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.2611</v>
+        <v>0.2577</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15289,7 +15281,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 26.1% (fair +283). Your call.</t>
+          <t>Model 25.8% (fair +288). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15325,13 +15317,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.7389</v>
+        <v>0.7423</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-283</v>
+        <v>-288</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15355,7 +15347,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 73.9% (fair -283). Your call.</t>
+          <t>Model 74.2% (fair -288). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15391,7 +15383,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4817</v>
+        <v>0.4807</v>
       </c>
       <c r="G77" s="14" t="n">
         <v>108</v>
@@ -15419,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15455,7 +15447,7 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5183</v>
+        <v>0.5193</v>
       </c>
       <c r="G78" s="14" t="n">
         <v>-108</v>
@@ -15483,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15519,10 +15511,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4432</v>
+        <v>0.4461</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="13">
@@ -15547,7 +15539,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15583,10 +15575,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5568</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-126</v>
+        <v>-124</v>
       </c>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="13">
@@ -15611,7 +15603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15647,10 +15639,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5835</v>
+        <v>0.5817</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="H81" s="15" t="n"/>
       <c r="I81" s="13">
@@ -15675,7 +15667,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15711,10 +15703,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4165</v>
+        <v>0.4183</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H82" s="15" t="n"/>
       <c r="I82" s="13">
@@ -15739,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15775,13 +15767,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.4777</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15805,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15841,13 +15833,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.5223</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-105</v>
+        <v>-109</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15871,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15907,13 +15899,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4687</v>
+        <v>0.4719</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15937,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15973,13 +15965,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5313</v>
+        <v>0.5281</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -16003,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16039,7 +16031,7 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4585381999999999</v>
+        <v>0.459</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>118</v>
@@ -16105,13 +16097,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5414618000000001</v>
+        <v>0.541</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>-118</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16171,10 +16163,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.457</v>
+        <v>0.4601</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>117</v>
@@ -16201,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16237,13 +16229,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.543</v>
+        <v>0.5399</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16267,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16435,10 +16427,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4843</v>
+        <v>0.4808</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>108</v>
@@ -16465,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16501,10 +16493,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5192</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-113</v>
@@ -16531,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16567,13 +16559,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4564</v>
+        <v>0.4623</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16597,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16633,13 +16625,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5436</v>
+        <v>0.5377</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-119</v>
+        <v>-116</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16663,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16699,10 +16691,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4258</v>
+        <v>0.4323</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>138</v>
@@ -16729,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 43.2% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16765,13 +16757,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5742</v>
+        <v>0.5677</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-135</v>
+        <v>-131</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-144</v>
+        <v>-133</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16795,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 56.8% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16831,10 +16823,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.416</v>
+        <v>0.4107</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>144</v>
@@ -16861,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16897,13 +16889,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.584</v>
+        <v>0.5893</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-140</v>
+        <v>-143</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16927,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16963,7 +16955,7 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.5016</v>
+        <v>0.5033000000000001</v>
       </c>
       <c r="G101" s="14" t="n">
         <v>-101</v>
@@ -16993,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17029,7 +17021,7 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.4984</v>
+        <v>0.4967</v>
       </c>
       <c r="G102" s="14" t="n">
         <v>101</v>
@@ -17059,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17095,10 +17087,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5988</v>
+        <v>0.6009</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-149</v>
+        <v>-151</v>
       </c>
       <c r="H103" s="15" t="n"/>
       <c r="I103" s="13">
@@ -17123,7 +17115,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17159,10 +17151,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4012</v>
+        <v>0.3991</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H104" s="15" t="n"/>
       <c r="I104" s="13">
@@ -17187,7 +17179,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17223,10 +17215,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5988</v>
+        <v>0.5945</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="H105" s="15" t="n"/>
       <c r="I105" s="13">
@@ -17251,7 +17243,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17287,10 +17279,10 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4012</v>
+        <v>0.4055</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H106" s="15" t="n"/>
       <c r="I106" s="13">
@@ -17315,7 +17307,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.6% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17351,10 +17343,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4216</v>
+        <v>0.4244</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H107" s="15" t="n"/>
       <c r="I107" s="13">
@@ -17379,7 +17371,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17415,10 +17407,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5784</v>
+        <v>0.5756</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="H108" s="15" t="n"/>
       <c r="I108" s="13">
@@ -17443,7 +17435,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17479,7 +17471,7 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4751</v>
+        <v>0.4753</v>
       </c>
       <c r="G109" s="14" t="n">
         <v>110</v>
@@ -17543,7 +17535,7 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5249</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="G110" s="14" t="n">
         <v>-110</v>
@@ -17607,10 +17599,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4852</v>
+        <v>0.4786</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="13">
@@ -17635,7 +17627,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17671,10 +17663,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5148</v>
+        <v>0.5214</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-106</v>
+        <v>-109</v>
       </c>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="13">
@@ -17699,7 +17691,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17882,7 +17874,7 @@
         <v>150</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -17948,7 +17940,7 @@
         <v>-150</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -18004,14 +17996,14 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 180.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6629721069956294</v>
+        <v>0.5964301472202969</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-197</v>
+        <v>-148</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>108</v>
@@ -18038,7 +18030,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 66.3% (fair -197). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -18070,17 +18062,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 180.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3370278930043706</v>
+        <v>0.4035698527797031</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>197</v>
+        <v>148</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -18104,7 +18096,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 33.7% (fair +197). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -18146,7 +18138,7 @@
         <v>-197</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -18212,7 +18204,7 @@
         <v>197</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -18278,7 +18270,7 @@
         <v>1157</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -18532,17 +18524,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -14</t>
+          <t>Minnesota Lynx -14.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.454</v>
+        <v>0.4256728939813748</v>
       </c>
       <c r="G15" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="H15" s="15" t="n">
         <v>120</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>111</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -18566,7 +18558,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -18598,17 +18590,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +14</t>
+          <t>Portland Fire +14.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5149</v>
+        <v>0.5743271060186252</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-106</v>
+        <v>-135</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -18632,7 +18624,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -18674,7 +18666,7 @@
         <v>370</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -18796,17 +18788,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 147</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5662</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-142</v>
+        <v>-131</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -18830,7 +18822,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -18862,17 +18854,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 147</t>
+          <t>Under 148.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3925999999999999</v>
+        <v>0.4338</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>-103</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -18896,7 +18888,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -18928,17 +18920,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -9.5</t>
+          <t>Golden State Valkyries -10.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5351367606222199</v>
+        <v>0.5037694772681063</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-115</v>
+        <v>-102</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -18962,7 +18954,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -18994,17 +18986,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics +9.5</t>
+          <t>Washington Mystics +10.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4648632393777801</v>
+        <v>0.4962305227318937</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>122</v>
+        <v>-105</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -19028,7 +19020,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -19527,22 +19519,22 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2493</v>
+        <v>0.2496</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3858</v>
+        <v>0.3861</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-101.82</v>
+        <v>-101.72</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-15.4</v>
+        <v>-15.34</v>
       </c>
       <c r="H5" s="24" t="n">
         <v>4.03</v>
@@ -19589,22 +19581,22 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>0.2417</v>
+        <v>0.2456</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>0.4348</v>
+        <v>0.4366</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>-2.08</v>
+        <v>-1.98</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>-3.02</v>
+        <v>-2.8</v>
       </c>
       <c r="H7" s="24" t="n">
         <v>-12.49</v>
@@ -19662,7 +19654,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=435, ECE 0.051 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=436, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -19795,16 +19787,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.6403</v>
+        <v>0.6401</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.54</v>
+        <v>0.5294</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.1003</v>
+        <v>-0.1106</v>
       </c>
     </row>
     <row r="23">
@@ -20118,13 +20110,13 @@
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
@@ -20414,13 +20406,13 @@
       </c>
       <c r="H74" s="35" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>15th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
@@ -20572,12 +20564,12 @@
       </c>
       <c r="I78" s="32" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="J78" s="36" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
@@ -20867,7 +20859,7 @@
       </c>
       <c r="H82" s="35" t="inlineStr">
         <is>
-          <t>13th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
@@ -21050,13 +21042,13 @@
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
       <c r="J70" s="33" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
@@ -21346,13 +21338,13 @@
       </c>
       <c r="H74" s="35" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>15th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
@@ -21504,12 +21496,12 @@
       </c>
       <c r="I78" s="32" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="J78" s="36" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
@@ -21799,7 +21791,7 @@
       </c>
       <c r="H82" s="35" t="inlineStr">
         <is>
-          <t>13th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>

--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 14:01</t>
+          <t>2026-07-18 14:13</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,250 +3031,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Toronto Blue Jays defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.953</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.953</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.894</v>
+        <v>4.571</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.354</v>
+        <v>7.792</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3338,22 +3259,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.979</v>
+        <v>7.894</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.208</v>
+        <v>1.354</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -3417,317 +3338,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.489000000000001</v>
+        <v>0.979</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.489000000000001</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.627</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.554</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Toronto Blue Jays offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.083</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.553</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.468</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.083</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.854</v>
+        <v>4.553</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.915</v>
+        <v>8.468</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3791,22 +3712,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>7.854</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.298</v>
+        <v>0.915</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -3870,72 +3791,151 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.938</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.458</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J82" s="33" t="inlineStr">
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.605</v>
+        <v>0.6057</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>150</v>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9895,22 +9895,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4162</v>
+        <v>0.5371</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>140</v>
+        <v>-116</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9961,22 +9961,22 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5216000000000001</v>
+        <v>0.4137</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-109</v>
+        <v>142</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4922</v>
+        <v>0.4945</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>120</v>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10432,10 +10432,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.395</v>
+        <v>0.3943</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>168</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12223,10 +12223,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.5151</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>104</v>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.4849</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-102</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4784</v>
+        <v>0.4629</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5216000000000001</v>
+        <v>0.5371</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-109</v>
+        <v>-116</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>112</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5838</v>
+        <v>0.5863</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-163</v>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4162</v>
+        <v>0.4137</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>170</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5092</v>
+        <v>0.506</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4908</v>
+        <v>0.494</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4807</v>
+        <v>0.4868</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5193</v>
+        <v>0.5132</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -16295,10 +16295,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4916</v>
+        <v>0.4868</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>102</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5084</v>
+        <v>0.5132</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-105</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16427,10 +16427,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.395</v>
+        <v>0.3943</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>168</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16493,10 +16493,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.605</v>
+        <v>0.6057</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-153</v>
+        <v>-154</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>150</v>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4938</v>
+        <v>0.495</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>-104</v>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16625,10 +16625,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5062</v>
+        <v>0.505</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>108</v>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5376</v>
+        <v>0.5281</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-116</v>
+        <v>-112</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>-120</v>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16757,10 +16757,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4624</v>
+        <v>0.4719</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>100</v>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5895</v>
+        <v>0.59</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>-144</v>
@@ -16889,7 +16889,7 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4105</v>
+        <v>0.41</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>144</v>
@@ -18011,10 +18011,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4876</v>
+        <v>0.5078</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>105</v>
+        <v>-103</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>100</v>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18077,10 +18077,10 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5124</v>
+        <v>0.4922</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-105</v>
+        <v>103</v>
       </c>
       <c r="H118" s="15" t="n">
         <v>-105</v>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18143,7 +18143,7 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3994</v>
+        <v>0.3995</v>
       </c>
       <c r="G119" s="14" t="n">
         <v>150</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6006</v>
+        <v>0.6005</v>
       </c>
       <c r="G120" s="14" t="n">
         <v>-150</v>
@@ -18275,7 +18275,7 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.446</v>
       </c>
       <c r="G121" s="14" t="n">
         <v>124</v>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18341,7 +18341,7 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.5534</v>
+        <v>0.554</v>
       </c>
       <c r="G122" s="14" t="n">
         <v>-124</v>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18407,10 +18407,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4905</v>
+        <v>0.4965</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>100</v>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18473,10 +18473,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5095000000000001</v>
+        <v>0.5035000000000001</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-104</v>
+        <v>-101</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>-110</v>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18539,10 +18539,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.3633</v>
+        <v>0.365</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>168</v>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18605,10 +18605,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.6367</v>
+        <v>0.635</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-175</v>
+        <v>-174</v>
       </c>
       <c r="H126" s="15" t="n">
         <v>-190</v>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -19067,10 +19067,10 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5078</v>
+        <v>0.5055000000000001</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H133" s="15" t="n">
         <v>-122</v>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19133,10 +19133,10 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4922</v>
+        <v>0.4945</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H134" s="15" t="n">
         <v>120</v>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19199,10 +19199,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.491</v>
+        <v>0.4693</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>100</v>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19265,10 +19265,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.509</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="H136" s="15" t="n">
         <v>-105</v>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19331,10 +19331,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5669</v>
+        <v>0.5686</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-131</v>
+        <v>-132</v>
       </c>
       <c r="H137" s="15" t="n">
         <v>-125</v>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 56.7% (fair -131). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19397,10 +19397,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4331</v>
+        <v>0.4314</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H138" s="15" t="n">
         <v>105</v>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19983,10 +19983,10 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4293</v>
+        <v>0.4244</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="13">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20047,10 +20047,10 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5707</v>
+        <v>0.5756</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H148" s="15" t="n"/>
       <c r="I148" s="13">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20239,10 +20239,10 @@
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>0.4786</v>
+        <v>0.4802</v>
       </c>
       <c r="G151" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="13">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="N151" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O151" s="15" t="n"/>
@@ -20303,10 +20303,10 @@
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.5214</v>
+        <v>0.5198</v>
       </c>
       <c r="G152" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H152" s="15" t="n"/>
       <c r="I152" s="13">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="N152" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O152" s="15" t="n"/>

--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10887075"/>
+    <ext cx="10125075" cy="10239375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10020300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 14:13</t>
+          <t>2026-07-18 15:18</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3971,903 +3971,903 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E65" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F65" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I65" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J65" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K65" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L65" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M65" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N65" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O65" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P65" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q65" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>4.012</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>5.591</v>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Colorado Rockies defense</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>9.532</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.012</v>
+        <v>0.518</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4</v>
+        <v>0.467</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>3.85</v>
+        <v>0.3</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>3.733</v>
+        <v>0.333</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="H70" s="35" t="inlineStr">
         <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J70" s="35" t="inlineStr">
         <is>
-          <t>21st</t>
+          <t>20th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>5.733</v>
+        <v>0.867</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.591</v>
+        <v>0.724</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>7.404</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs Cincinnati Reds defense</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>9.532</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+      <c r="A73" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B73" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C73" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D73" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E73" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F73" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I73" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J73" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K73" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L73" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M73" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N73" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O73" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P73" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q73" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.518</v>
+        <v>4.761</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.467</v>
+        <v>5.7</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.3</v>
+        <v>5.45</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.333</v>
+        <v>5.4</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="35" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>12th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>0.867</v>
+        <v>4.333</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>0.9</v>
+        <v>4.067</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>0.724</v>
+        <v>4.595</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp 1st Inn R/G</t>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs Cincinnati Reds defense</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>7.404</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.761</v>
+        <v>0.517</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>5.7</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>5.45</v>
+        <v>0.7</v>
       </c>
       <c r="E78" s="32" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="F78" s="32" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="H78" s="36" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
       <c r="J78" s="35" t="inlineStr">
         <is>
-          <t>12th</t>
+          <t>18th</t>
         </is>
       </c>
       <c r="K78" s="32" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="L78" s="32" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="M78" s="32" t="n">
-        <v>4.333</v>
+        <v>0.533</v>
       </c>
       <c r="N78" s="32" t="n">
-        <v>4.3</v>
+        <v>0.45</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>4.067</v>
+        <v>0.4</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.595</v>
+        <v>0.53</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>8.106</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>1.383</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>7.404</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="36" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5835,171 +5835,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.055</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.333</v>
+        <v>7.087</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5.33</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.087</v>
+        <v>1.022</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6063,22 +6142,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.022</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -6142,313 +6221,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.417</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.208</v>
+        <v>0.788</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H78" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.286</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.284</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H79" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>7.792</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>5.3</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.286</v>
+        <v>7.848</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6512,22 +6591,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>7.848</v>
+        <v>0.848</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -6591,147 +6670,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>0.848</v>
+        <v>8.304</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.518</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8.304</v>
+        <v>0.488</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7686,7 +7686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7703,423 +7703,580 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Boston Red Sox defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>4.553</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>2.967</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>3.881</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.778</v>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.391</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Boston Red Sox defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>1.217</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.553</v>
+        <v>0.518</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>4.267</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>4.75</v>
+        <v>0.65</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>4.133</v>
+        <v>0.4</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="H71" s="35" t="inlineStr">
         <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>2.8</v>
+        <v>0.533</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>2.85</v>
+        <v>0.45</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>2.967</v>
+        <v>0.433</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>3.881</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.391</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>1.217</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Boston Red Sox offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.244</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.587</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>0.518</v>
+        <v>4.333</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>0.5669999999999999</v>
+        <v>4.733</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>0.65</v>
+        <v>5.2</v>
       </c>
       <c r="E75" s="32" t="n">
-        <v>0.4</v>
+        <v>5.133</v>
       </c>
       <c r="F75" s="32" t="n">
-        <v>0.3</v>
+        <v>5.8</v>
       </c>
       <c r="G75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>5.6</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr">
@@ -8129,154 +8286,297 @@
       </c>
       <c r="J75" s="36" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="K75" s="32" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="L75" s="32" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="M75" s="32" t="n">
-        <v>0.533</v>
+        <v>4.4</v>
       </c>
       <c r="N75" s="32" t="n">
-        <v>0.45</v>
+        <v>3.75</v>
       </c>
       <c r="O75" s="32" t="n">
-        <v>0.433</v>
+        <v>3.967</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>0.6870000000000001</v>
+        <v>4.482</v>
       </c>
       <c r="Q75" s="34" t="inlineStr">
         <is>
-          <t>Opp 1st Inn R/G</t>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Boston Red Sox offense vs Tampa Bay Rays defense</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>8.239000000000001</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.333</v>
+        <v>0.41</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>4.733</v>
+        <v>0.633</v>
       </c>
       <c r="D79" s="32" t="n">
-        <v>5.2</v>
+        <v>0.85</v>
       </c>
       <c r="E79" s="32" t="n">
-        <v>5.133</v>
+        <v>0.867</v>
       </c>
       <c r="F79" s="32" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="G79" s="32" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="H79" s="33" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr">
@@ -8286,328 +8586,28 @@
       </c>
       <c r="J79" s="36" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K79" s="32" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="L79" s="32" t="n">
-        <v>4.9</v>
+        <v>0.3</v>
       </c>
       <c r="M79" s="32" t="n">
-        <v>4.4</v>
+        <v>0.467</v>
       </c>
       <c r="N79" s="32" t="n">
-        <v>3.75</v>
+        <v>0.45</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>3.967</v>
+        <v>0.367</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.482</v>
+        <v>0.482</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>8.304</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>1.444</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>8.239000000000001</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>7.778</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6664</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -199). Your call.</t>
+          <t>Model 66.6% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8986,7 +8986,7 @@
         <v>-208</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9225,12 +9225,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9240,17 +9240,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6684</v>
+        <v>0.6651</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-202</v>
+        <v>-199</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -202). Your call.</t>
+          <t>Model 66.5% (fair -199). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9286,37 +9286,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>San Francisco Giants @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.6683</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-154</v>
+        <v>-201</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9438,17 +9438,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.615</v>
+        <v>0.633</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-160</v>
+        <v>-172</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6312</v>
+        <v>0.6278</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-171</v>
+        <v>-169</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>102</v>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9550,7 +9550,7 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9574,13 +9574,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6278</v>
+        <v>0.5631</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-169</v>
+        <v>-129</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9636,17 +9636,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5656</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-130</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9687,32 +9687,32 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5200999999999999</v>
+        <v>0.534</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9753,12 +9753,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9768,17 +9768,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 148.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5632</v>
+        <v>0.4923</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-129</v>
+        <v>103</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9819,32 +9819,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Indiana Fever</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.534</v>
+        <v>0.5647</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-115</v>
+        <v>-130</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9895,22 +9895,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5371</v>
+        <v>0.4137</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-116</v>
+        <v>142</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9946,37 +9946,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Toronto Blue Jays</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4137</v>
+        <v>0.5117</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>142</v>
+        <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10012,17 +10012,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10032,11 +10032,11 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 13</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5517</v>
+        <v>0.551</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-123</v>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10102,10 +10102,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4945</v>
+        <v>0.4922</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>120</v>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
@@ -10159,22 +10159,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3999</v>
+        <v>0.5200999999999999</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>150</v>
+        <v>-108</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10215,32 +10215,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5337</v>
+        <v>0.3999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-114</v>
+        <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10281,32 +10281,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5281</v>
+        <v>0.4956</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-112</v>
+        <v>102</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10347,32 +10347,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5371</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-108</v>
+        <v>-116</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10423,22 +10423,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.3943</v>
+        <v>0.5221</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>154</v>
+        <v>-109</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4602000000000001</v>
+        <v>0.4581</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>122</v>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10705,10 +10705,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5397999999999999</v>
+        <v>0.5419</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-117</v>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10771,10 +10771,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6312</v>
+        <v>0.633</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>102</v>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3688</v>
+        <v>0.367</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>128</v>
@@ -10867,7 +10867,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.7% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10903,10 +10903,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3342</v>
+        <v>0.3336</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>175</v>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 33.4% (fair +199). Your call.</t>
+          <t>Model 33.4% (fair +200). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10969,10 +10969,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6664</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-199</v>
+        <v>-200</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>178</v>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 66.6% (fair -199). Your call.</t>
+          <t>Model 66.6% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4243</v>
+        <v>0.42</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11497,13 +11497,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5757</v>
+        <v>0.58</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-141</v>
+        <v>-138</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11559,17 +11559,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5337</v>
+        <v>0.4923</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-114</v>
+        <v>103</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -114). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11625,17 +11625,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4663</v>
+        <v>0.4207000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +114). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11695,13 +11695,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3934</v>
+        <v>0.3994</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +154). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11761,13 +11761,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6066</v>
+        <v>0.6006</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-154</v>
+        <v>-150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-153</v>
+        <v>-145</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11833,7 +11833,7 @@
         <v>195</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11899,7 +11899,7 @@
         <v>-195</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-120</v>
+        <v>-130</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11955,17 +11955,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.523</v>
+        <v>0.418</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-110</v>
+        <v>139</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-108</v>
+        <v>103</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12021,17 +12021,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.477</v>
+        <v>0.4956</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12091,13 +12091,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4472</v>
+        <v>0.4486</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5528</v>
+        <v>0.5514</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-124</v>
+        <v>-123</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12223,13 +12223,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5151</v>
+        <v>0.5159</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12289,13 +12289,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4849</v>
+        <v>0.4841</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12361,7 +12361,7 @@
         <v>116</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12427,7 +12427,7 @@
         <v>-116</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4808</v>
+        <v>0.4816</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>108</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12685,13 +12685,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.5184</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12747,17 +12747,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 13</t>
+          <t>Over 12.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3778</v>
+        <v>0.4801</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12813,17 +12813,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 13</t>
+          <t>Under 12.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5517</v>
+        <v>0.5199</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-123</v>
+        <v>-108</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4842</v>
+        <v>0.4854000000000001</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>100</v>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13081,13 +13081,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5158</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4803</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>111</v>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13213,13 +13213,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4349</v>
+        <v>0.4326</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.6137</v>
+        <v>0.6117</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-159</v>
+        <v>-158</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-167</v>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13345,10 +13345,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.3863</v>
+        <v>0.3883</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>163</v>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13411,13 +13411,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4839</v>
+        <v>0.4837</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>107</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13477,7 +13477,7 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5161</v>
+        <v>0.5163</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-107</v>
@@ -13543,13 +13543,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.385</v>
+        <v>0.3349</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 33.5% (fair +199). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.615</v>
+        <v>0.6651</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-160</v>
+        <v>-199</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>117</v>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 66.5% (fair -199). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6123</v>
+        <v>0.6151</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-158</v>
+        <v>-160</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>-153</v>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3877</v>
+        <v>0.3849</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>150</v>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13945,7 +13945,7 @@
         <v>153</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -14011,7 +14011,7 @@
         <v>-108</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -14203,13 +14203,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4719</v>
+        <v>0.4196</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14269,13 +14269,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5281</v>
+        <v>0.5804</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-112</v>
+        <v>-138</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14341,7 +14341,7 @@
         <v>130</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -14407,7 +14407,7 @@
         <v>-130</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -14599,13 +14599,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4666</v>
+        <v>0.4628</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14665,13 +14665,13 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5334</v>
+        <v>0.5372</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-114</v>
+        <v>-116</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.506</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-102</v>
+        <v>-108</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.494</v>
+        <v>0.4814</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15251,13 +15251,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.2577</v>
+        <v>0.258</v>
       </c>
       <c r="G75" s="14" t="n">
         <v>288</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15317,13 +15317,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6684</v>
+        <v>0.6683</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-202</v>
+        <v>-201</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 66.8% (fair -202). Your call.</t>
+          <t>Model 66.8% (fair -201). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.4817</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5183</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15511,7 +15511,7 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4461</v>
+        <v>0.4466</v>
       </c>
       <c r="G79" s="14" t="n">
         <v>124</v>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5538999999999999</v>
+        <v>0.5534</v>
       </c>
       <c r="G80" s="14" t="n">
         <v>-124</v>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15767,10 +15767,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4857</v>
+        <v>0.4881</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>100</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15833,13 +15833,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5143</v>
+        <v>0.5119</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15899,13 +15899,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4926</v>
+        <v>0.4948</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15965,13 +15965,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5074000000000001</v>
+        <v>0.5052</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.6211</v>
+        <v>0.6244</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-164</v>
+        <v>-166</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-162</v>
+        <v>-165</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.3789</v>
+        <v>0.3756</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16169,7 +16169,7 @@
         <v>138</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16295,13 +16295,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.4779</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,13 +16361,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5221</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-105</v>
+        <v>-109</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16427,13 +16427,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3943</v>
+        <v>0.369</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16493,13 +16493,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.631</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-154</v>
+        <v>-171</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>150</v>
+        <v>-200</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16559,13 +16559,13 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.495</v>
+        <v>0.4995000000000001</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.505</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16687,17 +16687,17 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5281</v>
+        <v>0.4405</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-112</v>
+        <v>127</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-120</v>
+        <v>-105</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16753,17 +16753,17 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4719</v>
+        <v>0.4727</v>
       </c>
       <c r="G98" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.59</v>
+        <v>0.5926</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-144</v>
+        <v>-145</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>-145</v>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.3% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16889,13 +16889,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.41</v>
+        <v>0.4074</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 40.7% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16955,10 +16955,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4605</v>
+        <v>0.468</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>113</v>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17021,13 +17021,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5395</v>
+        <v>0.532</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-117</v>
+        <v>-114</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-117</v>
+        <v>-105</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17068,32 +17068,32 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5248999999999999</v>
+        <v>0.4834</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-110</v>
+        <v>107</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-108</v>
+        <v>105</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17134,32 +17134,32 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4751</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>110</v>
+        <v>-107</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17200,32 +17200,32 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5024</v>
+        <v>0.6175</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-101</v>
+        <v>-161</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-110</v>
+        <v>-175</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 61.8% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17266,32 +17266,32 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4025</v>
+        <v>0.3825</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +148). Your call.</t>
+          <t>Model 38.2% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17342,22 +17342,22 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5896</v>
+        <v>0.5313</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-170</v>
+        <v>-113</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17408,22 +17408,22 @@
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4104</v>
+        <v>0.4687</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17464,32 +17464,32 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4808</v>
+        <v>0.5631</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>108</v>
+        <v>-129</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17530,32 +17530,32 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5192</v>
+        <v>0.4369</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-108</v>
+        <v>129</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-113</v>
+        <v>100</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17596,32 +17596,32 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5004</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-100</v>
+        <v>-141</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>100</v>
+        <v>-155</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17662,32 +17662,32 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4996</v>
+        <v>0.4147999999999999</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-110</v>
+        <v>145</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17738,22 +17738,22 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.3249</v>
+        <v>0.4843</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +208). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17804,22 +17804,22 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.5157</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-208</v>
+        <v>-106</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>164</v>
+        <v>-108</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17860,7 +17860,7 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -17870,22 +17870,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4513</v>
+        <v>0.4978</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17926,7 +17926,7 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
@@ -17936,22 +17936,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5487</v>
+        <v>0.5022</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-122</v>
+        <v>-101</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -18002,22 +18002,22 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.5078</v>
+        <v>0.3249</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-103</v>
+        <v>208</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>100</v>
+        <v>165</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 32.5% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
@@ -18068,22 +18068,22 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.4922</v>
+        <v>0.6751</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>103</v>
+        <v>-208</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-105</v>
+        <v>170</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18134,22 +18134,22 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals -1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.3995</v>
+        <v>0.4196</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18200,22 +18200,22 @@
       </c>
       <c r="D120" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.6005</v>
+        <v>0.5804</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-155</v>
+        <v>-113</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -18266,22 +18266,22 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.446</v>
+        <v>0.5046</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>124</v>
+        <v>-102</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
@@ -18332,22 +18332,22 @@
       </c>
       <c r="D122" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.554</v>
+        <v>0.4954</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-124</v>
+        <v>102</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-122</v>
+        <v>-104</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -18398,22 +18398,22 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Kansas City Royals -1.5</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4965</v>
+        <v>0.3873</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
@@ -18464,22 +18464,22 @@
       </c>
       <c r="D124" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5035000000000001</v>
+        <v>0.6127</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-101</v>
+        <v>-158</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-110</v>
+        <v>-180</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 61.3% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18530,22 +18530,22 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.365</v>
+        <v>0.446</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 36.5% (fair +174). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18596,22 +18596,22 @@
       </c>
       <c r="D126" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.635</v>
+        <v>0.554</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-174</v>
+        <v>-124</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-190</v>
+        <v>-122</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 63.5% (fair -174). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18652,32 +18652,32 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4133</v>
+        <v>0.5117</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>142</v>
+        <v>-105</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18718,32 +18718,32 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D128" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5867</v>
+        <v>0.4883</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-142</v>
+        <v>105</v>
       </c>
       <c r="H128" s="15" t="n">
-        <v>-144</v>
+        <v>100</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18784,32 +18784,32 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.5165</v>
+        <v>0.3639</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-107</v>
+        <v>175</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18850,32 +18850,32 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D130" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.6361</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>151</v>
+        <v>-175</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>-115</v>
+        <v>-190</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18926,22 +18926,22 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4152</v>
+        <v>0.4133</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18992,22 +18992,22 @@
       </c>
       <c r="D132" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5848</v>
+        <v>0.5867</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-141</v>
+        <v>-142</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-145</v>
+        <v>-144</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19031,7 +19031,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19048,32 +19048,32 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5055000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>-102</v>
+        <v>-123</v>
       </c>
       <c r="H133" s="15" t="n">
-        <v>-122</v>
+        <v>100</v>
       </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19114,32 +19114,32 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4945</v>
+        <v>0.449</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="H134" s="15" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19180,32 +19180,32 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4693</v>
+        <v>0.4152</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="H135" s="15" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 41.5% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19246,32 +19246,32 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.5848</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-113</v>
+        <v>-141</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-105</v>
+        <v>-145</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 58.5% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19322,22 +19322,22 @@
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5686</v>
+        <v>0.5078</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-132</v>
+        <v>-103</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19388,22 +19388,22 @@
       </c>
       <c r="D138" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4314</v>
+        <v>0.4922</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19444,31 +19444,33 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Over 11.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.6009</v>
+        <v>0.483</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-151</v>
-      </c>
-      <c r="H139" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>110</v>
+      </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
         <v/>
@@ -19491,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19508,31 +19510,33 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Under 11.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.517</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>151</v>
-      </c>
-      <c r="H140" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-105</v>
+      </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
         <v/>
@@ -19555,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19572,32 +19576,32 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.5178</v>
+        <v>0.5708</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>-107</v>
+        <v>-133</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>-108</v>
+        <v>-125</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -19621,7 +19625,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19638,32 +19642,32 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Cincinnati Reds -1.5</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.4292</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -19687,7 +19691,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19714,23 +19718,21 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.547</v>
+        <v>0.6009</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H143" s="15" t="n">
-        <v>-145</v>
-      </c>
+        <v>-151</v>
+      </c>
+      <c r="H143" s="15" t="n"/>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
         <v/>
@@ -19753,7 +19755,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19780,23 +19782,21 @@
       </c>
       <c r="D144" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.453</v>
+        <v>0.3991</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>121</v>
-      </c>
-      <c r="H144" s="15" t="n">
-        <v>125</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="H144" s="15" t="n"/>
       <c r="I144" s="13">
         <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
         <v/>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19983,10 +19983,10 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4244</v>
+        <v>0.4293</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H147" s="15" t="n"/>
       <c r="I147" s="13">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20047,10 +20047,10 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5756</v>
+        <v>0.5707</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-136</v>
+        <v>-133</v>
       </c>
       <c r="H148" s="15" t="n"/>
       <c r="I148" s="13">
@@ -20075,7 +20075,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20239,10 +20239,10 @@
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>0.4802</v>
+        <v>0.4786</v>
       </c>
       <c r="G151" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="13">
@@ -20267,7 +20267,7 @@
       </c>
       <c r="N151" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O151" s="15" t="n"/>
@@ -20303,10 +20303,10 @@
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.5198</v>
+        <v>0.5214</v>
       </c>
       <c r="G152" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H152" s="15" t="n"/>
       <c r="I152" s="13">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="N152" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O152" s="15" t="n"/>
@@ -20646,7 +20646,7 @@
         <v>-134</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -20712,7 +20712,7 @@
         <v>134</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -20910,7 +20910,7 @@
         <v>1157</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -21032,17 +21032,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 174</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.663616289416556</v>
+        <v>0.6528185358973585</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-197</v>
+        <v>-188</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -197). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -21098,14 +21098,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 173.5</t>
+          <t>Under 174</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.336383710583444</v>
+        <v>0.3254814641026415</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 33.6% (fair +197). Your call.</t>
+          <t>Model 32.5% (fair +207). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -21164,17 +21164,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -13.5</t>
+          <t>Minnesota Lynx -14</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.456735522554393</v>
+        <v>0.4411589559011642</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -21230,17 +21230,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Portland Fire +14</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.543264477445607</v>
+        <v>0.5277410440988358</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-119</v>
+        <v>-112</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -21372,7 +21372,7 @@
         <v>-370</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-115</v>
+        <v>-110</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -21432,10 +21432,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5632</v>
+        <v>0.5656</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-129</v>
+        <v>-130</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -21462,7 +21462,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 56.6% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21498,13 +21498,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4368</v>
+        <v>0.4344</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 43.4% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -21560,17 +21560,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -8.5</t>
+          <t>Golden State Valkyries -9</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5662870953684607</v>
+        <v>0.5507510321853004</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-131</v>
+        <v>-123</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>106</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -21626,14 +21626,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics +8.5</t>
+          <t>Washington Mystics +9</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4337129046315393</v>
+        <v>0.4180489678146996</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>122</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>

--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10429875"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10687050"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 17:03</t>
+          <t>2026-07-18 18:03</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,899 +2103,899 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H68" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.807</v>
-      </c>
-      <c r="Q68" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>9.319000000000001</v>
-      </c>
-      <c r="Q69" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.933</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.276999999999999</v>
+        <v>4.807</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>9.319000000000001</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Q73" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.276999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.535</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H72" s="35" t="inlineStr">
+      <c r="H75" s="35" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.553</v>
       </c>
-      <c r="Q72" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.409</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.789</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>7.234</v>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.918</v>
-      </c>
-      <c r="Q77" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="C78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>0.918</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.409</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>5.8</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>9.061</v>
+        <v>4.789</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>7.234</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.918</v>
+      </c>
+      <c r="Q80" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="Q81" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>8.426</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.518</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H83" s="36" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="36" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.523</v>
       </c>
-      <c r="Q80" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -3014,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3031,250 +3031,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Toronto Blue Jays defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.953</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>4.571</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.953</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.894</v>
+        <v>4.571</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.354</v>
+        <v>7.792</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -3338,22 +3259,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>0.979</v>
+        <v>7.894</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>9.208</v>
+        <v>1.354</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -3417,317 +3338,317 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>9.489000000000001</v>
+        <v>0.979</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>9.208</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.489000000000001</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.627</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.65</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="J75" s="36" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.554</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Toronto Blue Jays offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.083</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>3.933</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.553</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.468</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.083</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H79" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.854</v>
+        <v>4.553</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.915</v>
+        <v>8.468</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -3791,22 +3712,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>7.854</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.298</v>
+        <v>0.915</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -3870,72 +3791,151 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>7.938</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.298</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>7.938</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.458</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J82" s="33" t="inlineStr">
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4886,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4903,250 +4903,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.593</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.593</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.625</v>
+        <v>5</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.271</v>
+        <v>8.208</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5210,22 +5131,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.292</v>
+        <v>7.625</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.917</v>
+        <v>1.271</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -5289,313 +5210,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.417</v>
+        <v>1.292</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.482</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.635</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.686</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.885</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.833</v>
+        <v>4.686</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.417</v>
+        <v>8.083</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5659,22 +5580,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>8.833</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.729</v>
+        <v>1.417</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -5738,68 +5659,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.6820000000000001</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7031000000000001</v>
+        <v>0.7046</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-237</v>
+        <v>-239</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>178</v>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 70.3% (fair -237). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8890,17 +8890,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6687000000000001</v>
+        <v>0.6751</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-202</v>
+        <v>-208</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8956,17 +8956,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.6687000000000001</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-208</v>
+        <v>-202</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9108,17 +9108,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Los Angeles Dodgers +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.6541</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-154</v>
+        <v>-189</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9154,17 +9154,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9174,14 +9174,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers +1.5</t>
+          <t>Los Angeles Dodgers +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6221</v>
+        <v>0.6386000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-165</v>
+        <v>-177</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>167</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9220,7 +9220,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6001000000000001</v>
+        <v>0.6057</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-150</v>
+        <v>-154</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9291,32 +9291,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6221</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-176</v>
+        <v>-165</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9357,32 +9357,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6228</v>
+        <v>0.6001000000000001</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-165</v>
+        <v>-150</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9418,17 +9418,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>San Francisco Giants @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9438,17 +9438,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5765</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-136</v>
+        <v>-181</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9489,32 +9489,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals -1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4093</v>
+        <v>0.6089</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>144</v>
+        <v>-156</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>203</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9555,12 +9555,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9570,14 +9570,14 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.6228</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>102</v>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -9636,17 +9636,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5912000000000001</v>
+        <v>0.6114999999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-145</v>
+        <v>-157</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6015</v>
+        <v>0.6112</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-151</v>
+        <v>-157</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>102</v>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9748,17 +9748,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9768,17 +9768,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5631</v>
+        <v>0.5912000000000001</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-129</v>
+        <v>-145</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6128</v>
+        <v>0.5631</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-158</v>
+        <v>-129</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9880,17 +9880,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9900,14 +9900,14 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5867</v>
+        <v>0.5898</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-142</v>
+        <v>-144</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>100</v>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9946,17 +9946,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Atlanta Dream</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9966,17 +9966,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 173.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5787</v>
+        <v>0.5867</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-137</v>
+        <v>-142</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10012,17 +10012,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Chicago Sky @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10032,17 +10032,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5629</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10083,32 +10083,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.491</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>104</v>
+        <v>-113</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10149,12 +10149,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Sparks @ Dallas Wings</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10164,17 +10164,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 181.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5728</v>
+        <v>0.5332</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-134</v>
+        <v>-114</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-104</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10210,17 +10210,17 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Toronto Blue Jays</t>
+          <t>Chicago Sky @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Chicago Sky +10.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4153</v>
+        <v>0.5415</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>141</v>
+        <v>-118</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10276,17 +10276,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5228</v>
+        <v>0.5693</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-110</v>
+        <v>-132</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10342,17 +10342,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10362,17 +10362,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5117</v>
+        <v>0.4931</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-105</v>
+        <v>103</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5200999999999999</v>
+        <v>0.5647</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-108</v>
+        <v>-130</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10495,7 +10495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P152"/>
+  <dimension ref="A1:P158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4823</v>
+        <v>0.4824000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>107</v>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5177</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-107</v>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6015</v>
+        <v>0.6112</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-151</v>
+        <v>-157</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>102</v>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3985</v>
+        <v>0.3888</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>128</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2969</v>
+        <v>0.2954</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>175</v>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 29.7% (fair +237). Your call.</t>
+          <t>Model 29.5% (fair +239). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7031000000000001</v>
+        <v>0.7046</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-237</v>
+        <v>-239</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 70.3% (fair -237). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11431,10 +11431,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.422</v>
+        <v>0.4185</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>146</v>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11497,10 +11497,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.578</v>
+        <v>0.5815</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-137</v>
+        <v>-139</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-138</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11563,10 +11563,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.491</v>
+        <v>0.4931</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>130</v>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4219</v>
+        <v>0.4198</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-104</v>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11695,10 +11695,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3999</v>
+        <v>0.4017</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11761,10 +11761,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6001000000000001</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-150</v>
+        <v>-149</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-145</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.4813</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>108</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.5187</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-108</v>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4815</v>
+        <v>0.4837</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>102</v>
@@ -12781,7 +12781,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5185</v>
+        <v>0.5163</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-108</v>
+        <v>-107</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-104</v>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5997</v>
+        <v>0.601</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-138</v>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12949,10 +12949,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4003</v>
+        <v>0.399</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>138</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.4814</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.2856</v>
+        <v>0.2789</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>109</v>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 28.6% (fair +250). Your call.</t>
+          <t>Model 27.9% (fair +259). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-176</v>
+        <v>-181</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>113</v>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15364,12 +15364,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Washington Nationals @ Athletics</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -15379,14 +15379,14 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4758</v>
+        <v>0.4466</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15428,12 +15428,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Washington Nationals @ Athletics</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>02:05</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -15443,14 +15443,14 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5242</v>
+        <v>0.5534</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-110</v>
+        <v>-124</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15492,12 +15492,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Detroit Tigers @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>02:07</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -15507,14 +15507,14 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.5817</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>124</v>
+        <v>-139</v>
       </c>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="13">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15556,12 +15556,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Detroit Tigers @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>02:05</t>
+          <t>02:07</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -15571,14 +15571,14 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5534</v>
+        <v>0.4183</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-124</v>
+        <v>139</v>
       </c>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="13">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15620,12 +15620,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Los Angeles Angels</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>02:07</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -15635,14 +15635,14 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.4868</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-139</v>
+        <v>105</v>
       </c>
       <c r="H81" s="15" t="n"/>
       <c r="I81" s="13">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15684,12 +15684,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Los Angeles Angels</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>02:07</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -15699,14 +15699,14 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4183</v>
+        <v>0.5132</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>139</v>
+        <v>-105</v>
       </c>
       <c r="H82" s="15" t="n"/>
       <c r="I82" s="13">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15767,13 +15767,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4873</v>
+        <v>0.4905</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15833,10 +15833,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5127</v>
+        <v>0.5095</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>104</v>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.6237</v>
+        <v>0.6165</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-166</v>
+        <v>-161</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,13 +16097,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.3763</v>
+        <v>0.3835</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16144,12 +16144,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4196</v>
+        <v>0.4762999999999999</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16210,12 +16210,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -16225,17 +16225,17 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5804</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-138</v>
+        <v>-110</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 58.0% (fair -138). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16276,12 +16276,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -16291,17 +16291,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.3819</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16342,12 +16342,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -16357,17 +16357,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5332</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-109</v>
+        <v>-114</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16408,12 +16408,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -16423,17 +16423,17 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3943</v>
+        <v>0.3459</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 34.6% (fair +189). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16474,12 +16474,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -16489,17 +16489,17 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Los Angeles Dodgers +1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.6541</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-154</v>
+        <v>-189</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16540,12 +16540,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -16555,17 +16555,17 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5034000000000001</v>
+        <v>0.4724</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-101</v>
+        <v>112</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16606,12 +16606,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -16621,17 +16621,17 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4966</v>
+        <v>0.5276</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>101</v>
+        <v>-112</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>115</v>
+        <v>-106</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16672,12 +16672,12 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -16691,13 +16691,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4405</v>
+        <v>0.3115</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 31.1% (fair +221). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16738,12 +16738,12 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
@@ -16757,10 +16757,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.6089</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>112</v>
+        <v>-156</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>117</v>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16804,12 +16804,12 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -16819,17 +16819,17 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies +1.5</t>
+          <t>New York Yankees -1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.587</v>
+        <v>0.3614</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-142</v>
+        <v>177</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-143</v>
+        <v>156</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16870,12 +16870,12 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Philadelphia Phillies</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D100" s="20" t="inlineStr">
@@ -16885,17 +16885,17 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>New York Mets -1.5</t>
+          <t>Los Angeles Dodgers +1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.413</v>
+        <v>0.6386000000000001</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>142</v>
+        <v>-177</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -16951,14 +16951,14 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4661</v>
+        <v>0.4196</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>113</v>
@@ -16985,7 +16985,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -17002,7 +17002,7 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
@@ -17017,17 +17017,17 @@
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5339</v>
+        <v>0.5804</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-115</v>
+        <v>-138</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -17087,13 +17087,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4779</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-100</v>
+        <v>109</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
@@ -17153,13 +17153,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5221</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>100</v>
+        <v>-109</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-125</v>
+        <v>105</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17200,7 +17200,7 @@
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.6162</v>
+        <v>0.3943</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-161</v>
+        <v>154</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-175</v>
+        <v>178</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
@@ -17281,17 +17281,17 @@
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.3838</v>
+        <v>0.6057</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>161</v>
+        <v>-154</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>145</v>
+        <v>178</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17332,12 +17332,12 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -17347,14 +17347,14 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5071</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-114</v>
+        <v>-103</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>-113</v>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
@@ -17413,17 +17413,17 @@
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4682</v>
+        <v>0.4929</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17464,12 +17464,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -17479,17 +17479,17 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.5631</v>
+        <v>0.462</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>-129</v>
+        <v>116</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17530,12 +17530,12 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -17545,17 +17545,17 @@
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4369</v>
+        <v>0.4508</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17596,12 +17596,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -17611,17 +17611,17 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>Philadelphia Phillies +1.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5831</v>
+        <v>0.5879</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-140</v>
+        <v>-143</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-155</v>
+        <v>-143</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17662,12 +17662,12 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>New York Mets @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -17677,17 +17677,17 @@
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates -1.5</t>
+          <t>New York Mets -1.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4169</v>
+        <v>0.4121</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17728,12 +17728,12 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -17743,14 +17743,14 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4843</v>
+        <v>0.4685</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>108</v>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17794,12 +17794,12 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
@@ -17809,17 +17809,17 @@
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5315</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-106</v>
+        <v>-113</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17860,12 +17860,12 @@
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -17879,13 +17879,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.5228</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>-110</v>
+        <v>-100</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 50.0% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17926,12 +17926,12 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D116" s="20" t="inlineStr">
@@ -17945,13 +17945,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4772</v>
+        <v>0.4995000000000001</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>105</v>
+        <v>-125</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17992,12 +17992,12 @@
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -18007,17 +18007,17 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>Atlanta Braves +1.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.3249</v>
+        <v>0.6162</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>208</v>
+        <v>-161</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>165</v>
+        <v>-175</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +208). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18058,12 +18058,12 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D118" s="20" t="inlineStr">
@@ -18073,17 +18073,17 @@
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.3838</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-208</v>
+        <v>161</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18124,12 +18124,12 @@
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -18139,17 +18139,17 @@
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4464</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>124</v>
+        <v>-114</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>117</v>
+        <v>-113</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18190,12 +18190,12 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D120" s="20" t="inlineStr">
@@ -18205,17 +18205,17 @@
       </c>
       <c r="E120" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5536</v>
+        <v>0.4682</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>-124</v>
+        <v>114</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>-117</v>
+        <v>113</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18256,12 +18256,12 @@
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -18271,17 +18271,17 @@
       </c>
       <c r="E121" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5042</v>
+        <v>0.5631</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-102</v>
+        <v>-129</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18322,12 +18322,12 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D122" s="20" t="inlineStr">
@@ -18337,17 +18337,17 @@
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4958</v>
+        <v>0.4369</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18388,12 +18388,12 @@
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -18403,17 +18403,17 @@
       </c>
       <c r="E123" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals -1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.4093</v>
+        <v>0.5873</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>144</v>
+        <v>-142</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>203</v>
+        <v>-156</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +144). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18454,12 +18454,12 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D124" s="20" t="inlineStr">
@@ -18469,17 +18469,17 @@
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Pittsburgh Pirates -1.5</t>
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.5907</v>
+        <v>0.4127</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>-144</v>
+        <v>142</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>-170</v>
+        <v>150</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -144). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -18535,17 +18535,17 @@
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.451</v>
+        <v>0.4843</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="H125" s="15" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I125" s="13">
         <f>IF($H$125="","",IF($H$125&lt;0,-$H$125/(-$H$125+100),100/($H$125+100)))</f>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18586,7 +18586,7 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
@@ -18601,17 +18601,17 @@
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.549</v>
+        <v>0.5157</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-122</v>
+        <v>-106</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-122</v>
+        <v>-108</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -18671,13 +18671,13 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.5117</v>
+        <v>0.5228</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>-105</v>
+        <v>-110</v>
       </c>
       <c r="H127" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I127" s="13">
         <f>IF($H$127="","",IF($H$127&lt;0,-$H$127/(-$H$127+100),100/($H$127+100)))</f>
@@ -18701,7 +18701,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
@@ -18737,13 +18737,13 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4883</v>
+        <v>0.4772</v>
       </c>
       <c r="G128" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H128" s="15" t="n">
         <v>105</v>
-      </c>
-      <c r="H128" s="15" t="n">
-        <v>110</v>
       </c>
       <c r="I128" s="13">
         <f>IF($H$128="","",IF($H$128&lt;0,-$H$128/(-$H$128+100),100/($H$128+100)))</f>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -18799,17 +18799,17 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.3662</v>
+        <v>0.3249</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="H129" s="15" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I129" s="13">
         <f>IF($H$129="","",IF($H$129&lt;0,-$H$129/(-$H$129+100),100/($H$129+100)))</f>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 32.5% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Milwaukee Brewers</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
@@ -18865,17 +18865,17 @@
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins +1.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.6337999999999999</v>
+        <v>0.6751</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-173</v>
+        <v>-208</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>-182</v>
+        <v>178</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18916,12 +18916,12 @@
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
@@ -18931,17 +18931,17 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.4126</v>
+        <v>0.4464</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="H131" s="15" t="n">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="I131" s="13">
         <f>IF($H$131="","",IF($H$131&lt;0,-$H$131/(-$H$131+100),100/($H$131+100)))</f>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18982,12 +18982,12 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D132" s="20" t="inlineStr">
@@ -18997,17 +18997,17 @@
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.5874</v>
+        <v>0.5536</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-142</v>
+        <v>-124</v>
       </c>
       <c r="H132" s="15" t="n">
-        <v>-144</v>
+        <v>-117</v>
       </c>
       <c r="I132" s="13">
         <f>IF($H$132="","",IF($H$132&lt;0,-$H$132/(-$H$132+100),100/($H$132+100)))</f>
@@ -19031,7 +19031,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -19048,12 +19048,12 @@
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
@@ -19063,17 +19063,17 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5524</v>
+        <v>0.5019</v>
       </c>
       <c r="G133" s="14" t="n">
-        <v>-123</v>
+        <v>-101</v>
       </c>
       <c r="H133" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I133" s="13">
         <f>IF($H$133="","",IF($H$133&lt;0,-$H$133/(-$H$133+100),100/($H$133+100)))</f>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19114,12 +19114,12 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D134" s="20" t="inlineStr">
@@ -19129,17 +19129,17 @@
       </c>
       <c r="E134" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4476</v>
+        <v>0.4981</v>
       </c>
       <c r="G134" s="14" t="n">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="H134" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I134" s="13">
         <f>IF($H$134="","",IF($H$134&lt;0,-$H$134/(-$H$134+100),100/($H$134+100)))</f>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19180,12 +19180,12 @@
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
@@ -19195,17 +19195,17 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Kansas City Royals -1.5</t>
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.415</v>
+        <v>0.388</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H135" s="15" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="I135" s="13">
         <f>IF($H$135="","",IF($H$135&lt;0,-$H$135/(-$H$135+100),100/($H$135+100)))</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19246,12 +19246,12 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D136" s="20" t="inlineStr">
@@ -19261,17 +19261,17 @@
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>San Diego Padres +1.5</t>
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.585</v>
+        <v>0.612</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-141</v>
+        <v>-158</v>
       </c>
       <c r="H136" s="15" t="n">
-        <v>-145</v>
+        <v>-170</v>
       </c>
       <c r="I136" s="13">
         <f>IF($H$136="","",IF($H$136&lt;0,-$H$136/(-$H$136+100),100/($H$136+100)))</f>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19312,12 +19312,12 @@
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
@@ -19327,17 +19327,17 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5055000000000001</v>
+        <v>0.4495</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-102</v>
+        <v>122</v>
       </c>
       <c r="H137" s="15" t="n">
-        <v>-122</v>
+        <v>122</v>
       </c>
       <c r="I137" s="13">
         <f>IF($H$137="","",IF($H$137&lt;0,-$H$137/(-$H$137+100),100/($H$137+100)))</f>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19378,12 +19378,12 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D138" s="20" t="inlineStr">
@@ -19393,17 +19393,17 @@
       </c>
       <c r="E138" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4945</v>
+        <v>0.5505</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>102</v>
+        <v>-122</v>
       </c>
       <c r="H138" s="15" t="n">
-        <v>120</v>
+        <v>-122</v>
       </c>
       <c r="I138" s="13">
         <f>IF($H$138="","",IF($H$138&lt;0,-$H$138/(-$H$138+100),100/($H$138+100)))</f>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19444,12 +19444,12 @@
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -19459,17 +19459,17 @@
       </c>
       <c r="E139" s="12" t="inlineStr">
         <is>
-          <t>Over 11.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.4235</v>
+        <v>0.5117</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>136</v>
+        <v>-105</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19510,12 +19510,12 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D140" s="20" t="inlineStr">
@@ -19525,17 +19525,17 @@
       </c>
       <c r="E140" s="20" t="inlineStr">
         <is>
-          <t>Under 11.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.5765</v>
+        <v>0.4883</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-136</v>
+        <v>105</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19576,12 +19576,12 @@
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -19591,17 +19591,17 @@
       </c>
       <c r="E141" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.573</v>
+        <v>0.3609</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>-134</v>
+        <v>177</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>-122</v>
+        <v>178</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 36.1% (fair +177). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19642,12 +19642,12 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Colorado Rockies</t>
+          <t>Miami Marlins @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D142" s="20" t="inlineStr">
@@ -19657,17 +19657,17 @@
       </c>
       <c r="E142" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds -1.5</t>
+          <t>Miami Marlins +1.5</t>
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.427</v>
+        <v>0.6391</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>134</v>
+        <v>-177</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>113</v>
+        <v>-185</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 63.9% (fair -177). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19708,12 +19708,12 @@
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
@@ -19723,16 +19723,18 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F143" s="13" t="n">
-        <v>0.599</v>
+        <v>0.4069</v>
       </c>
       <c r="G143" s="14" t="n">
-        <v>-149</v>
-      </c>
-      <c r="H143" s="15" t="n"/>
+        <v>146</v>
+      </c>
+      <c r="H143" s="15" t="n">
+        <v>150</v>
+      </c>
       <c r="I143" s="13">
         <f>IF($H$143="","",IF($H$143&lt;0,-$H$143/(-$H$143+100),100/($H$143+100)))</f>
         <v/>
@@ -19755,7 +19757,7 @@
       </c>
       <c r="N143" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 40.7% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O143" s="15" t="n"/>
@@ -19772,12 +19774,12 @@
       </c>
       <c r="B144" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Athletics</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D144" s="20" t="inlineStr">
@@ -19787,16 +19789,18 @@
       </c>
       <c r="E144" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F144" s="13" t="n">
-        <v>0.401</v>
+        <v>0.5931</v>
       </c>
       <c r="G144" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="H144" s="15" t="n"/>
+        <v>-146</v>
+      </c>
+      <c r="H144" s="15" t="n">
+        <v>-150</v>
+      </c>
       <c r="I144" s="13">
         <f>IF($H$144="","",IF($H$144&lt;0,-$H$144/(-$H$144+100),100/($H$144+100)))</f>
         <v/>
@@ -19819,7 +19823,7 @@
       </c>
       <c r="N144" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 59.3% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O144" s="15" t="n"/>
@@ -19836,31 +19840,33 @@
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.5976</v>
+        <v>0.5494</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>-149</v>
-      </c>
-      <c r="H145" s="15" t="n"/>
+        <v>-122</v>
+      </c>
+      <c r="H145" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I145" s="13">
         <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
         <v/>
@@ -19883,7 +19889,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19900,31 +19906,33 @@
       </c>
       <c r="B146" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Los Angeles Angels</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D146" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E146" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4024</v>
+        <v>0.4506</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>149</v>
-      </c>
-      <c r="H146" s="15" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I146" s="13">
         <f>IF($H$146="","",IF($H$146&lt;0,-$H$146/(-$H$146+100),100/($H$146+100)))</f>
         <v/>
@@ -19947,7 +19955,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19964,31 +19972,33 @@
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4244</v>
+        <v>0.418</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>136</v>
-      </c>
-      <c r="H147" s="15" t="n"/>
+        <v>139</v>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>142</v>
+      </c>
       <c r="I147" s="13">
         <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
         <v/>
@@ -20011,7 +20021,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20028,31 +20038,33 @@
       </c>
       <c r="B148" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C148" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D148" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E148" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5756</v>
+        <v>0.5820000000000001</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H148" s="15" t="n"/>
+        <v>-139</v>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>-145</v>
+      </c>
       <c r="I148" s="13">
         <f>IF($H$148="","",IF($H$148&lt;0,-$H$148/(-$H$148+100),100/($H$148+100)))</f>
         <v/>
@@ -20075,7 +20087,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20092,12 +20104,12 @@
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
@@ -20107,14 +20119,14 @@
       </c>
       <c r="E149" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F149" s="13" t="n">
-        <v>0.4753</v>
+        <v>0.4592</v>
       </c>
       <c r="G149" s="14" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H149" s="15" t="n"/>
       <c r="I149" s="13">
@@ -20139,7 +20151,7 @@
       </c>
       <c r="N149" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O149" s="15" t="n"/>
@@ -20156,12 +20168,12 @@
       </c>
       <c r="B150" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+          <t>Cincinnati Reds @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C150" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D150" s="20" t="inlineStr">
@@ -20171,14 +20183,14 @@
       </c>
       <c r="E150" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="G150" s="14" t="n">
-        <v>-110</v>
+        <v>-118</v>
       </c>
       <c r="H150" s="15" t="n"/>
       <c r="I150" s="13">
@@ -20203,7 +20215,7 @@
       </c>
       <c r="N150" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O150" s="15" t="n"/>
@@ -20220,12 +20232,12 @@
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Washington Nationals @ Athletics</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
@@ -20235,14 +20247,14 @@
       </c>
       <c r="E151" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>0.4802</v>
+        <v>0.599</v>
       </c>
       <c r="G151" s="14" t="n">
-        <v>108</v>
+        <v>-149</v>
       </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="13">
@@ -20267,7 +20279,7 @@
       </c>
       <c r="N151" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O151" s="15" t="n"/>
@@ -20284,12 +20296,12 @@
       </c>
       <c r="B152" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Washington Nationals @ Athletics</t>
         </is>
       </c>
       <c r="C152" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D152" s="20" t="inlineStr">
@@ -20299,14 +20311,14 @@
       </c>
       <c r="E152" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.5198</v>
+        <v>0.401</v>
       </c>
       <c r="G152" s="14" t="n">
-        <v>-108</v>
+        <v>149</v>
       </c>
       <c r="H152" s="15" t="n"/>
       <c r="I152" s="13">
@@ -20331,7 +20343,7 @@
       </c>
       <c r="N152" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O152" s="15" t="n"/>
@@ -20340,9 +20352,393 @@
         <v/>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B153" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="D153" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E153" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F153" s="13" t="n">
+        <v>0.5976</v>
+      </c>
+      <c r="G153" s="14" t="n">
+        <v>-149</v>
+      </c>
+      <c r="H153" s="15" t="n"/>
+      <c r="I153" s="13">
+        <f>IF($H$153="","",IF($H$153&lt;0,-$H$153/(-$H$153+100),100/($H$153+100)))</f>
+        <v/>
+      </c>
+      <c r="J153" s="16">
+        <f>IF($H$153="","",$F$153*IF($H$153&lt;0,-100/$H$153,$H$153/100)-(1-$F$153))</f>
+        <v/>
+      </c>
+      <c r="K153" s="17">
+        <f>IF($H$153="","",MAX(0,($F$153*IF($H$153&lt;0,-100/$H$153,$H$153/100)-(1-$F$153))/IF($H$153&lt;0,-100/$H$153,$H$153/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L153" s="18">
+        <f>IF($H$153="","",ROUND(MIN($K$153,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M153" s="12">
+        <f>IF($J$153="","",IF($J$153&lt;0,"Pass",IF($J$153&lt;'Settings'!$B$4,"Thin",IF($J$153&lt;0.06,"✅ Sharp band",IF($J$153&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N153" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.8% (fair -149). Your call.</t>
+        </is>
+      </c>
+      <c r="O153" s="15" t="n"/>
+      <c r="P153" s="16">
+        <f>IF(OR($H$153="",$O$153=""),"",(1+IF($H$153&lt;0,-100/$H$153,$H$153/100))/(1+IF($O$153&lt;0,-100/$O$153,$O$153/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="C154" s="20" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="D154" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E154" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="G154" s="14" t="n">
+        <v>149</v>
+      </c>
+      <c r="H154" s="15" t="n"/>
+      <c r="I154" s="13">
+        <f>IF($H$154="","",IF($H$154&lt;0,-$H$154/(-$H$154+100),100/($H$154+100)))</f>
+        <v/>
+      </c>
+      <c r="J154" s="16">
+        <f>IF($H$154="","",$F$154*IF($H$154&lt;0,-100/$H$154,$H$154/100)-(1-$F$154))</f>
+        <v/>
+      </c>
+      <c r="K154" s="17">
+        <f>IF($H$154="","",MAX(0,($F$154*IF($H$154&lt;0,-100/$H$154,$H$154/100)-(1-$F$154))/IF($H$154&lt;0,-100/$H$154,$H$154/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L154" s="18">
+        <f>IF($H$154="","",ROUND(MIN($K$154,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M154" s="12">
+        <f>IF($J$154="","",IF($J$154&lt;0,"Pass",IF($J$154&lt;'Settings'!$B$4,"Thin",IF($J$154&lt;0.06,"✅ Sharp band",IF($J$154&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N154" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.2% (fair +149). Your call.</t>
+        </is>
+      </c>
+      <c r="O154" s="15" t="n"/>
+      <c r="P154" s="16">
+        <f>IF(OR($H$154="",$O$154=""),"",(1+IF($H$154&lt;0,-100/$H$154,$H$154/100))/(1+IF($O$154&lt;0,-100/$O$154,$O$154/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F155" s="13" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="G155" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H155" s="15" t="n"/>
+      <c r="I155" s="13">
+        <f>IF($H$155="","",IF($H$155&lt;0,-$H$155/(-$H$155+100),100/($H$155+100)))</f>
+        <v/>
+      </c>
+      <c r="J155" s="16">
+        <f>IF($H$155="","",$F$155*IF($H$155&lt;0,-100/$H$155,$H$155/100)-(1-$F$155))</f>
+        <v/>
+      </c>
+      <c r="K155" s="17">
+        <f>IF($H$155="","",MAX(0,($F$155*IF($H$155&lt;0,-100/$H$155,$H$155/100)-(1-$F$155))/IF($H$155&lt;0,-100/$H$155,$H$155/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L155" s="18">
+        <f>IF($H$155="","",ROUND(MIN($K$155,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M155" s="12">
+        <f>IF($J$155="","",IF($J$155&lt;0,"Pass",IF($J$155&lt;'Settings'!$B$4,"Thin",IF($J$155&lt;0.06,"✅ Sharp band",IF($J$155&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N155" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.9% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O155" s="15" t="n"/>
+      <c r="P155" s="16">
+        <f>IF(OR($H$155="",$O$155=""),"",(1+IF($H$155&lt;0,-100/$H$155,$H$155/100))/(1+IF($O$155&lt;0,-100/$O$155,$O$155/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D156" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E156" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="G156" s="14" t="n">
+        <v>-133</v>
+      </c>
+      <c r="H156" s="15" t="n"/>
+      <c r="I156" s="13">
+        <f>IF($H$156="","",IF($H$156&lt;0,-$H$156/(-$H$156+100),100/($H$156+100)))</f>
+        <v/>
+      </c>
+      <c r="J156" s="16">
+        <f>IF($H$156="","",$F$156*IF($H$156&lt;0,-100/$H$156,$H$156/100)-(1-$F$156))</f>
+        <v/>
+      </c>
+      <c r="K156" s="17">
+        <f>IF($H$156="","",MAX(0,($F$156*IF($H$156&lt;0,-100/$H$156,$H$156/100)-(1-$F$156))/IF($H$156&lt;0,-100/$H$156,$H$156/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L156" s="18">
+        <f>IF($H$156="","",ROUND(MIN($K$156,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M156" s="12">
+        <f>IF($J$156="","",IF($J$156&lt;0,"Pass",IF($J$156&lt;'Settings'!$B$4,"Thin",IF($J$156&lt;0.06,"✅ Sharp band",IF($J$156&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N156" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.1% (fair -133). Your call.</t>
+        </is>
+      </c>
+      <c r="O156" s="15" t="n"/>
+      <c r="P156" s="16">
+        <f>IF(OR($H$156="",$O$156=""),"",(1+IF($H$156&lt;0,-100/$H$156,$H$156/100))/(1+IF($O$156&lt;0,-100/$O$156,$O$156/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B157" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E157" s="12" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="G157" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H157" s="15" t="n"/>
+      <c r="I157" s="13">
+        <f>IF($H$157="","",IF($H$157&lt;0,-$H$157/(-$H$157+100),100/($H$157+100)))</f>
+        <v/>
+      </c>
+      <c r="J157" s="16">
+        <f>IF($H$157="","",$F$157*IF($H$157&lt;0,-100/$H$157,$H$157/100)-(1-$F$157))</f>
+        <v/>
+      </c>
+      <c r="K157" s="17">
+        <f>IF($H$157="","",MAX(0,($F$157*IF($H$157&lt;0,-100/$H$157,$H$157/100)-(1-$F$157))/IF($H$157&lt;0,-100/$H$157,$H$157/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L157" s="18">
+        <f>IF($H$157="","",ROUND(MIN($K$157,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M157" s="12">
+        <f>IF($J$157="","",IF($J$157&lt;0,"Pass",IF($J$157&lt;'Settings'!$B$4,"Thin",IF($J$157&lt;0.06,"✅ Sharp band",IF($J$157&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N157" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.5% (fair +110). Your call.</t>
+        </is>
+      </c>
+      <c r="O157" s="15" t="n"/>
+      <c r="P157" s="16">
+        <f>IF(OR($H$157="",$O$157=""),"",(1+IF($H$157&lt;0,-100/$H$157,$H$157/100))/(1+IF($O$157&lt;0,-100/$O$157,$O$157/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C158" s="20" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="D158" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E158" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="n">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="G158" s="14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H158" s="15" t="n"/>
+      <c r="I158" s="13">
+        <f>IF($H$158="","",IF($H$158&lt;0,-$H$158/(-$H$158+100),100/($H$158+100)))</f>
+        <v/>
+      </c>
+      <c r="J158" s="16">
+        <f>IF($H$158="","",$F$158*IF($H$158&lt;0,-100/$H$158,$H$158/100)-(1-$F$158))</f>
+        <v/>
+      </c>
+      <c r="K158" s="17">
+        <f>IF($H$158="","",MAX(0,($F$158*IF($H$158&lt;0,-100/$H$158,$H$158/100)-(1-$F$158))/IF($H$158&lt;0,-100/$H$158,$H$158/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L158" s="18">
+        <f>IF($H$158="","",ROUND(MIN($K$158,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M158" s="12">
+        <f>IF($J$158="","",IF($J$158&lt;0,"Pass",IF($J$158&lt;'Settings'!$B$4,"Thin",IF($J$158&lt;0.06,"✅ Sharp band",IF($J$158&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N158" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.5% (fair -110). Your call.</t>
+        </is>
+      </c>
+      <c r="O158" s="15" t="n"/>
+      <c r="P158" s="16">
+        <f>IF(OR($H$158="",$O$158=""),"",(1+IF($H$158&lt;0,-100/$H$158,$H$158/100))/(1+IF($O$158&lt;0,-100/$O$158,$O$158/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J152">
+  <conditionalFormatting sqref="J5:J158">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -20508,13 +20904,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4</v>
+        <v>0.4703000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -20538,7 +20934,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20574,10 +20970,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>120</v>
@@ -20604,7 +21000,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -20646,7 +21042,7 @@
         <v>-111</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -20712,7 +21108,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -20910,7 +21306,7 @@
         <v>1157</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -21164,17 +21560,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -13.5</t>
+          <t>Minnesota Lynx -14</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4716</v>
+        <v>0.4411589559011642</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -21198,7 +21594,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -21230,17 +21626,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +13.5</t>
+          <t>Portland Fire +14</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5284</v>
+        <v>0.5277410440988358</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-112</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -21428,17 +21824,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 149</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6299665315792587</v>
+        <v>0.5693</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-170</v>
+        <v>-132</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -21462,7 +21858,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21494,17 +21890,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 149</t>
+          <t>Under 148.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3478334684207413</v>
+        <v>0.4307</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>102</v>
+        <v>-102</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -21528,7 +21924,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 34.8% (fair +187). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -21560,17 +21956,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -9</t>
+          <t>Golden State Valkyries -8.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5507510321853004</v>
+        <v>0.5662870953684607</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-123</v>
+        <v>-131</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -21594,7 +21990,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -21626,14 +22022,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics +9</t>
+          <t>Washington Mystics +8.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4180489678146996</v>
+        <v>0.4337129046315393</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>122</v>
@@ -21660,7 +22056,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -21768,7 +22164,7 @@
         <v>-312</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-110</v>
+        <v>-115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -21828,10 +22224,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5728</v>
+        <v>0.6308546079454266</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-134</v>
+        <v>-171</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>-104</v>
@@ -21858,7 +22254,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.3% (fair -134). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -21894,13 +22290,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4272</v>
+        <v>0.3691453920545734</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -21924,7 +22320,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 42.7% (fair +134). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -21960,10 +22356,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4902</v>
+        <v>0.4704989272572607</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>100</v>
@@ -21990,7 +22386,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -22026,13 +22422,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5098</v>
+        <v>0.5295010727427393</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -22056,7 +22452,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -22224,13 +22620,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5787</v>
+        <v>0.5629</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-137</v>
+        <v>-129</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -22254,7 +22650,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -22290,13 +22686,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4213</v>
+        <v>0.4371</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>108</v>
+        <v>-105</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -22320,7 +22716,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -22356,10 +22752,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3941557224036433</v>
+        <v>0.4585</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-106</v>
@@ -22386,7 +22782,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22422,13 +22818,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6058442775963567</v>
+        <v>0.5415</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-154</v>
+        <v>-118</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -22452,7 +22848,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -22616,17 +23012,17 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.6128</v>
+        <v>0.5898</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-158</v>
+        <v>-144</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -22650,7 +23046,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -22682,17 +23078,17 @@
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Under 163.5</t>
+          <t>Under 165.5</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.3872</v>
+        <v>0.4102</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -22716,7 +23112,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -22752,13 +23148,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4632</v>
+        <v>0.4602</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -22782,7 +23178,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -22818,10 +23214,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.5398000000000001</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>106</v>
@@ -22848,7 +23244,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -22963,28 +23359,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2495</v>
+        <v>0.2493</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3907</v>
+        <v>0.3914</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-94.90000000000001</v>
+        <v>-95.11</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-14.21</v>
+        <v>-14.15</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5409</v>
+        <v>0.5406</v>
       </c>
     </row>
     <row r="6">
@@ -22994,28 +23390,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2499</v>
+        <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3849</v>
+        <v>0.3856</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-93.70999999999999</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-15.75</v>
+        <v>-15.68</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5586</v>
+        <v>0.5581</v>
       </c>
     </row>
     <row r="7">
@@ -23098,7 +23494,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=438, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=440, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -23212,16 +23608,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5431</v>
+        <v>0.543</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5258</v>
+        <v>0.5306</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0173</v>
+        <v>-0.0124</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10648950"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 18:03</t>
+          <t>2026-07-18 19:02</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4903,171 +4903,250 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles offense vs Houston Astros defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>4.593</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>4.967</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.593</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.967</v>
+        <v>8.208</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5</v>
+        <v>7.625</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.208</v>
+        <v>1.271</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5131,22 +5210,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>7.625</v>
+        <v>1.292</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>1.271</v>
+        <v>8.917</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -5210,313 +5289,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>1.292</v>
+        <v>8.417</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.917</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.482</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>8.417</v>
+        <v>0.635</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="36" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Baltimore Orioles defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Baltimore Orioles defense</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>4.885</v>
+      </c>
+      <c r="C78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>4.686</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
+        <v>8.083</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>3.867</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.686</v>
+        <v>8.833</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5580,22 +5659,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.833</v>
+        <v>1.062</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -5659,147 +5738,68 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>1.062</v>
+        <v>8</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="32" t="n">
-        <v>7.729</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M82" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N82" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O82" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P82" s="32" t="n">
-        <v>8</v>
+        <v>0.459</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7046</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-239</v>
+        <v>-238</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>178</v>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 70.5% (fair -239). Your call.</t>
+          <t>Model 70.4% (fair -238). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8890,17 +8890,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles @ Houston Astros</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.6687000000000001</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-208</v>
+        <v>-202</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 66.9% (fair -202). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8956,17 +8956,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8976,17 +8976,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6687000000000001</v>
+        <v>0.6751</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-202</v>
+        <v>-208</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 66.9% (fair -202). Your call.</t>
+          <t>Model 67.5% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6541</v>
+        <v>0.6585</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-189</v>
+        <v>-193</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>167</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 65.8% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6386000000000001</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-177</v>
+        <v>-175</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>167</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9442,10 +9442,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6381</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-181</v>
+        <v>-176</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9504,17 +9504,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6089</v>
+        <v>0.646</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-156</v>
+        <v>-182</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 64.6% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9550,17 +9550,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9570,17 +9570,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6228</v>
+        <v>0.5989</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-165</v>
+        <v>-149</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9621,12 +9621,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9636,14 +9636,14 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.6228</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>102</v>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6112</v>
+        <v>0.6179</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-157</v>
+        <v>-162</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>102</v>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -9768,17 +9768,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5912000000000001</v>
+        <v>0.6114999999999999</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-145</v>
+        <v>-157</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9814,17 +9814,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9834,17 +9834,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5631</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-129</v>
+        <v>-142</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9885,12 +9885,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9900,17 +9900,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5898</v>
+        <v>0.5516</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-144</v>
+        <v>-123</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9946,17 +9946,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
+          <t>Connecticut Sun @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9966,14 +9966,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5867</v>
+        <v>0.5886</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>100</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10012,17 +10012,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Atlanta Dream</t>
+          <t>Portland Fire @ Minnesota Lynx</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10032,17 +10032,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 173.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5629</v>
+        <v>0.5879</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-129</v>
+        <v>-143</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>108</v>
+        <v>-102</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10078,37 +10078,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Indiana Fever</t>
+          <t>Chicago Sky @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Chicago Sky +10.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5403</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-113</v>
+        <v>-118</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5332</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10210,37 +10210,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Atlanta Dream</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +10.5</t>
+          <t>Over 148.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.5705</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-118</v>
+        <v>-133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10281,12 +10281,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 148.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5693</v>
+        <v>0.4945</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-132</v>
+        <v>102</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10347,32 +10347,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.5359</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>103</v>
+        <v>-115</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6112</v>
+        <v>0.6179</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-157</v>
+        <v>-162</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>102</v>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3888</v>
+        <v>0.3821</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>128</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2954</v>
+        <v>0.2959</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>175</v>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 29.5% (fair +239). Your call.</t>
+          <t>Model 29.6% (fair +238). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7046</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-239</v>
+        <v>-238</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 70.5% (fair -239). Your call.</t>
+          <t>Model 70.4% (fair -238). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11563,10 +11563,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4931</v>
+        <v>0.4945</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>130</v>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11629,10 +11629,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4198</v>
+        <v>0.4185000000000001</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>-104</v>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 42.0% (fair +138). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4017</v>
+        <v>0.4011</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>149</v>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.5989</v>
       </c>
       <c r="G22" s="14" t="n">
         <v>-149</v>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11827,10 +11827,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.2811455999999998</v>
+        <v>0.25926</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>156</v>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 28.1% (fair +256). Your call.</t>
+          <t>Model 25.9% (fair +286). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11893,10 +11893,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.7188544000000002</v>
+        <v>0.74074</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-256</v>
+        <v>-286</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-130</v>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 71.9% (fair -256). Your call.</t>
+          <t>Model 74.1% (fair -286). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.414</v>
+        <v>0.4144</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>103</v>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4997000000000001</v>
+        <v>0.4993</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>100</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4489</v>
+        <v>0.4509</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>125</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5510999999999999</v>
+        <v>0.5490999999999999</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12223,10 +12223,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5159</v>
+        <v>0.5206</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>102</v>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4841</v>
+        <v>0.4794</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-103</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4762</v>
+        <v>0.4683</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>122</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5238</v>
+        <v>0.5317000000000001</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-110</v>
+        <v>-114</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>100</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5847</v>
+        <v>0.5838</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-141</v>
+        <v>-140</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-163</v>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4153</v>
+        <v>0.4162</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>170</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4813</v>
+        <v>0.4815</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>108</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5187</v>
+        <v>0.5185</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>-108</v>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12751,7 +12751,7 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.4836</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>107</v>
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.5164</v>
       </c>
       <c r="G38" s="14" t="n">
         <v>-107</v>
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.601</v>
+        <v>0.5988</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-151</v>
+        <v>-149</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-138</v>
@@ -12913,7 +12913,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12949,10 +12949,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.399</v>
+        <v>0.4012</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>138</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4837</v>
+        <v>0.4805</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>-102</v>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5163</v>
+        <v>0.5195</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>104</v>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3349</v>
+        <v>0.3398</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>108</v>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 33.5% (fair +199). Your call.</t>
+          <t>Model 34.0% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5912000000000001</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-145</v>
+        <v>-142</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>108</v>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.612</v>
+        <v>0.6131</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>-158</v>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 61.3% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.388</v>
+        <v>0.3869</v>
       </c>
       <c r="G52" s="14" t="n">
         <v>158</v>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.2789</v>
+        <v>0.2853</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>109</v>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 27.9% (fair +259). Your call.</t>
+          <t>Model 28.5% (fair +251). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6381</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-181</v>
+        <v>-176</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>113</v>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4466</v>
+        <v>0.4281</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5534</v>
+        <v>0.5719</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-124</v>
+        <v>-134</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5817</v>
+        <v>0.5776</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-139</v>
+        <v>-137</v>
       </c>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="13">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4183</v>
+        <v>0.4224</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="13">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15639,10 +15639,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4868</v>
+        <v>0.4807</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H81" s="15" t="n"/>
       <c r="I81" s="13">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5132</v>
+        <v>0.5193</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H82" s="15" t="n"/>
       <c r="I82" s="13">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15767,7 +15767,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4905</v>
+        <v>0.4903999999999999</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>104</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15833,7 +15833,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5095</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>-104</v>
@@ -15863,7 +15863,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4948</v>
+        <v>0.4845</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>113</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15965,10 +15965,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.5155000000000001</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-102</v>
+        <v>-106</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>105</v>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16031,13 +16031,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.6165</v>
+        <v>0.623</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-161</v>
+        <v>-165</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,10 +16097,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.3835</v>
+        <v>0.377</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>178</v>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16163,10 +16163,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4762999999999999</v>
+        <v>0.4778</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>104</v>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16229,13 +16229,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5222</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16295,10 +16295,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.3819</v>
+        <v>0.386</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>100</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5332</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>117</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16427,10 +16427,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3459</v>
+        <v>0.3415</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>156</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 34.6% (fair +189). Your call.</t>
+          <t>Model 34.2% (fair +193). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16493,10 +16493,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6541</v>
+        <v>0.6585</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-189</v>
+        <v>-193</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>167</v>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 65.8% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4724</v>
+        <v>0.474</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>104</v>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16625,13 +16625,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5276</v>
+        <v>0.526</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-106</v>
+        <v>-104</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.3115</v>
+        <v>0.3204</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>100</v>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 31.1% (fair +221). Your call.</t>
+          <t>Model 32.0% (fair +212). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16757,10 +16757,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.6089</v>
+        <v>0.5989</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-156</v>
+        <v>-149</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>117</v>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.3614</v>
+        <v>0.3634</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>156</v>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.3% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.6386000000000001</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-177</v>
+        <v>-175</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>167</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.7% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -17351,7 +17351,7 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5071</v>
+        <v>0.5066999999999999</v>
       </c>
       <c r="G107" s="14" t="n">
         <v>-103</v>
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4929</v>
+        <v>0.4933</v>
       </c>
       <c r="G108" s="14" t="n">
         <v>103</v>
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.462</v>
+        <v>0.4358</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>100</v>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17549,10 +17549,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4508</v>
+        <v>0.4774</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>115</v>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 47.7% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17615,10 +17615,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5879</v>
+        <v>0.5935</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-143</v>
+        <v>-146</v>
       </c>
       <c r="H111" s="15" t="n">
         <v>-143</v>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4121</v>
+        <v>0.4065</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H112" s="15" t="n">
         <v>133</v>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17747,13 +17747,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4685</v>
+        <v>0.4488576</v>
       </c>
       <c r="G113" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="H113" s="15" t="n">
         <v>113</v>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>108</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17813,13 +17813,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5315</v>
+        <v>0.5511424</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-113</v>
+        <v>-123</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-110</v>
+        <v>-102</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17879,10 +17879,10 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4851</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>-100</v>
+        <v>106</v>
       </c>
       <c r="H115" s="15" t="n">
         <v>105</v>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17945,13 +17945,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5149</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18011,10 +18011,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.6162</v>
+        <v>0.6207</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-161</v>
+        <v>-164</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>-175</v>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18077,13 +18077,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.3838</v>
+        <v>0.3793</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18143,10 +18143,10 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5354</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H119" s="15" t="n">
         <v>-113</v>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18209,13 +18209,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4682</v>
+        <v>0.4646</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18275,13 +18275,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5631</v>
+        <v>0.5516</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-129</v>
+        <v>-123</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18341,10 +18341,10 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4369</v>
+        <v>0.4484</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>100</v>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18407,7 +18407,7 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5873</v>
+        <v>0.5865</v>
       </c>
       <c r="G123" s="14" t="n">
         <v>-142</v>
@@ -18473,7 +18473,7 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4127</v>
+        <v>0.4135</v>
       </c>
       <c r="G124" s="14" t="n">
         <v>142</v>
@@ -18539,10 +18539,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4843</v>
+        <v>0.4822</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>108</v>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5157</v>
+        <v>0.5178</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-108</v>
+        <v>-111</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18875,7 +18875,7 @@
         <v>-208</v>
       </c>
       <c r="H130" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I130" s="13">
         <f>IF($H$130="","",IF($H$130&lt;0,-$H$130/(-$H$130+100),100/($H$130+100)))</f>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5019</v>
+        <v>0.5032</v>
       </c>
       <c r="G133" s="14" t="n">
         <v>-101</v>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4981</v>
+        <v>0.4968</v>
       </c>
       <c r="G134" s="14" t="n">
         <v>101</v>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19199,10 +19199,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.388</v>
+        <v>0.3915</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>163</v>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 39.1% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19265,10 +19265,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.612</v>
+        <v>0.6085</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-158</v>
+        <v>-155</v>
       </c>
       <c r="H136" s="15" t="n">
         <v>-170</v>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 60.9% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.5117</v>
+        <v>0.4961</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>-105</v>
+        <v>102</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>108</v>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19529,13 +19529,13 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.4883</v>
+        <v>0.5039</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="H140" s="15" t="n">
-        <v>105</v>
+        <v>-102</v>
       </c>
       <c r="I140" s="13">
         <f>IF($H$140="","",IF($H$140&lt;0,-$H$140/(-$H$140+100),100/($H$140+100)))</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19595,10 +19595,10 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.3609</v>
+        <v>0.3618</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>178</v>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 36.1% (fair +177). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19661,13 +19661,13 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.6391</v>
+        <v>0.6382</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-177</v>
+        <v>-176</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-185</v>
+        <v>-182</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 63.9% (fair -177). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19859,13 +19859,13 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.5494</v>
+        <v>0.646</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>-122</v>
+        <v>-182</v>
       </c>
       <c r="H145" s="15" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I145" s="13">
         <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 64.6% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19925,10 +19925,10 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.4506</v>
+        <v>0.354</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>100</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 35.4% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19991,10 +19991,10 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.418</v>
+        <v>0.4169</v>
       </c>
       <c r="G147" s="14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H147" s="15" t="n">
         <v>142</v>
@@ -20021,7 +20021,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 41.7% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20057,10 +20057,10 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5820000000000001</v>
+        <v>0.5831</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="H148" s="15" t="n">
         <v>-145</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 58.3% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20123,7 +20123,7 @@
         </is>
       </c>
       <c r="F149" s="13" t="n">
-        <v>0.4592</v>
+        <v>0.4597</v>
       </c>
       <c r="G149" s="14" t="n">
         <v>118</v>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="N149" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O149" s="15" t="n"/>
@@ -20187,7 +20187,7 @@
         </is>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5403</v>
       </c>
       <c r="G150" s="14" t="n">
         <v>-118</v>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="N150" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O150" s="15" t="n"/>
@@ -20904,13 +20904,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4703000000000001</v>
+        <v>0.4641</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20970,13 +20970,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5359</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -21036,13 +21036,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5269667031772712</v>
+        <v>0.5202</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -21102,13 +21102,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4730332968227288</v>
+        <v>0.4798</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -21174,7 +21174,7 @@
         <v>-197</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -21240,7 +21240,7 @@
         <v>197</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -21306,7 +21306,7 @@
         <v>1157</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -21372,7 +21372,7 @@
         <v>-1157</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -21432,13 +21432,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5867</v>
+        <v>0.5879</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -21462,7 +21462,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -21498,10 +21498,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4133</v>
+        <v>0.4121</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>108</v>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -21570,7 +21570,7 @@
         <v>127</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -21636,7 +21636,7 @@
         <v>-112</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -21828,10 +21828,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5693</v>
+        <v>0.5705</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>100</v>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21894,13 +21894,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4307</v>
+        <v>0.4295</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -21966,7 +21966,7 @@
         <v>-131</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -22616,14 +22616,14 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 180.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5629</v>
+        <v>0.6194808686056472</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-129</v>
+        <v>-163</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>108</v>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 61.9% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -22682,17 +22682,17 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 180.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4371</v>
+        <v>0.3805191313943528</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -22716,7 +22716,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 38.1% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -22752,13 +22752,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4585</v>
+        <v>0.4597</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>118</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-106</v>
+        <v>-108</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22818,7 +22818,7 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5415</v>
+        <v>0.5403</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>-118</v>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -23016,10 +23016,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5898</v>
+        <v>0.5886</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-144</v>
+        <v>-143</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>100</v>
@@ -23046,7 +23046,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -23082,13 +23082,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4102</v>
+        <v>0.4114</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -23144,17 +23144,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury -4.5</t>
+          <t>Phoenix Mercury -3.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4602</v>
+        <v>0.4799</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>100</v>
+        <v>-105</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -23210,17 +23210,17 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun +4.5</t>
+          <t>Connecticut Sun +3.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5201</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -23359,28 +23359,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>0.2493</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3914</v>
+        <v>0.3941</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-95.11</v>
+        <v>-93.16</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-14.15</v>
+        <v>-13.7</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5406</v>
+        <v>0.5404</v>
       </c>
     </row>
     <row r="6">
@@ -23390,28 +23390,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3856</v>
+        <v>0.3888</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-93.93000000000001</v>
+        <v>-91.97</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-15.68</v>
+        <v>-15.15</v>
       </c>
       <c r="H6" s="24" t="n">
         <v>5.59</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5581</v>
+        <v>0.5577</v>
       </c>
     </row>
     <row r="7">
@@ -23494,7 +23494,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=440, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=443, ECE 0.051 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -23570,16 +23570,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>0.3662</v>
+        <v>0.3667</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.5263</v>
+        <v>0.5385</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.1602</v>
+        <v>0.1718</v>
       </c>
     </row>
     <row r="20">
@@ -23608,16 +23608,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.543</v>
+        <v>0.5429</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5306</v>
+        <v>0.533</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0124</v>
+        <v>-0.009900000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -23627,16 +23627,16 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>0.6401</v>
+        <v>0.6395</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.5294</v>
+        <v>0.5385</v>
       </c>
       <c r="E22" s="27" t="n">
-        <v>-0.1106</v>
+        <v>-0.1011</v>
       </c>
     </row>
     <row r="23">

--- a/data/output/workbook/2026-07-18.xlsx
+++ b/data/output/workbook/2026-07-18.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10915650"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10953750"/>
+    <ext cx="10125075" cy="10306050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18 19:02</t>
+          <t>2026-07-18 20:04</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4903,250 +4903,171 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Baltimore Orioles offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>4.593</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.593</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="36" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.967</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>7.625</v>
+        <v>5</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.271</v>
+        <v>8.208</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -5210,22 +5131,22 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.292</v>
+        <v>7.625</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.917</v>
+        <v>1.271</v>
       </c>
       <c r="C73" s="32" t="inlineStr">
         <is>
@@ -5289,313 +5210,313 @@
         </is>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.417</v>
+        <v>1.292</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>8.917</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="32" t="n">
+      <c r="B75" s="32" t="n">
         <v>0.482</v>
       </c>
-      <c r="C74" s="32" t="n">
+      <c r="C75" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D74" s="32" t="n">
+      <c r="D75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E74" s="32" t="n">
+      <c r="E75" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F74" s="32" t="n">
+      <c r="F75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G74" s="32" t="n">
+      <c r="G75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H74" s="36" t="inlineStr">
+      <c r="H75" s="36" t="inlineStr">
         <is>
           <t>28th</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.635</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Baltimore Orioles defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="30" t="inlineStr">
+      <c r="F78" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="30" t="inlineStr">
+      <c r="G78" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="30" t="inlineStr">
+      <c r="H78" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="30" t="inlineStr">
+      <c r="I78" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="30" t="inlineStr">
+      <c r="J78" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="30" t="inlineStr">
+      <c r="K78" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="30" t="inlineStr">
+      <c r="L78" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="30" t="inlineStr">
+      <c r="M78" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="30" t="inlineStr">
+      <c r="N78" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="30" t="inlineStr">
+      <c r="O78" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="30" t="inlineStr">
+      <c r="P78" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="30" t="inlineStr">
+      <c r="Q78" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>4.885</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>4.686</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.885</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>5.267</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>3.867</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.833</v>
+        <v>4.686</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.417</v>
+        <v>8.083</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -5659,22 +5580,22 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>1.062</v>
+        <v>8.833</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.729</v>
+        <v>1.417</v>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
@@ -5738,68 +5659,147 @@
         </is>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8</v>
+        <v>1.062</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="32" t="n">
+      <c r="B83" s="32" t="n">
         <v>0.6820000000000001</v>
       </c>
-      <c r="C82" s="32" t="n">
+      <c r="C83" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="D82" s="32" t="n">
+      <c r="D83" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E82" s="32" t="n">
+      <c r="E83" s="32" t="n">
         <v>0.467</v>
       </c>
-      <c r="F82" s="32" t="n">
+      <c r="F83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G82" s="32" t="n">
+      <c r="G83" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="I83" s="32" t="inlineStr"/>
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K82" s="32" t="n">
+      <c r="K83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L82" s="32" t="n">
+      <c r="L83" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M82" s="32" t="n">
+      <c r="M83" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N82" s="32" t="n">
+      <c r="N83" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O82" s="32" t="n">
+      <c r="O83" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P82" s="32" t="n">
+      <c r="P83" s="32" t="n">
         <v>0.459</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5835,171 +5835,250 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>San Diego Padres offense vs Kansas City Royals defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.055</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.055</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>6.333</v>
+        <v>7.087</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P70" s="32" t="n">
-        <v>5.33</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.087</v>
+        <v>1.022</v>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
@@ -6063,22 +6142,22 @@
         </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.022</v>
+        <v>8.348000000000001</v>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
@@ -6142,313 +6221,313 @@
         </is>
       </c>
       <c r="P72" s="32" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.348000000000001</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.417</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>0.767</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>1</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.208</v>
+        <v>0.788</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs San Diego Padres defense</t>
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.284</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>4.286</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.284</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>5.033</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>7.792</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="O78" s="32" t="n">
-        <v>5.3</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="32" t="n">
-        <v>4.286</v>
+        <v>7.848</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
@@ -6512,22 +6591,22 @@
         </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.848</v>
+        <v>0.848</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
@@ -6591,147 +6670,68 @@
         </is>
       </c>
       <c r="P80" s="32" t="n">
-        <v>0.848</v>
+        <v>8.304</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.518</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>0.667</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.304</v>
+        <v>0.488</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6750,7 +6750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6767,907 +6767,907 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>St. Louis Cardinals offense vs Arizona Diamondbacks defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.488</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.412</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>St. Louis Cardinals offense vs Arizona Diamondbacks defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>7.826</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>8.188000000000001</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4.488</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D71" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E71" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F71" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G71" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>8.196</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.1</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P71" s="32" t="n">
-        <v>4.412</v>
+        <v>7.146</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="36" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="Q72" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks offense vs St. Louis Cardinals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.447</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.442</v>
+      </c>
+      <c r="Q76" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
-        <v>7.826</v>
-      </c>
-      <c r="C72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.188000000000001</v>
-      </c>
-      <c r="Q72" s="34" t="inlineStr">
+      <c r="B77" s="32" t="n">
+        <v>8.542</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>8.651999999999999</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
-        <v>1.109</v>
-      </c>
-      <c r="C73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
+      <c r="B78" s="32" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>8.196</v>
-      </c>
-      <c r="C74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>7.146</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks offense vs St. Louis Cardinals defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>4.447</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>4.367</v>
-      </c>
-      <c r="D79" s="32" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E79" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="F79" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G79" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L79" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M79" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N79" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>4.667</v>
+        <v>7.354</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P79" s="32" t="n">
-        <v>4.442</v>
+        <v>7.739</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8.542</v>
-      </c>
-      <c r="C80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.541</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>0.467</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.651999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="C81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>1.043</v>
-      </c>
-      <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>7.354</v>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="32" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="C83" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D83" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E83" s="32" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F83" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="I83" s="32" t="inlineStr"/>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K83" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M83" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N83" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O83" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="P83" s="32" t="n">
-        <v>0.542</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.7048</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-238</v>
+        <v>-239</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>178</v>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 70.4% (fair -238). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.6724</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-208</v>
+        <v>-205</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>170</v>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 67.2% (fair -205). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6442</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-189</v>
+        <v>-181</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>178</v>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6585</v>
+        <v>0.6547000000000001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-193</v>
+        <v>-190</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>167</v>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 65.8% (fair -193). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6359</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-175</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9220,17 +9220,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9240,17 +9240,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Texas Rangers +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.6208</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-154</v>
+        <v>-164</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9306,17 +9306,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers +1.5</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6221</v>
+        <v>0.598</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-165</v>
+        <v>-149</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9357,32 +9357,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>San Francisco Giants @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6001000000000001</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-150</v>
+        <v>-176</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9418,17 +9418,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:08</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9438,14 +9438,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6381</v>
+        <v>0.6341</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-176</v>
+        <v>-173</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Los Angeles Dodgers @ New York Yankees</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9504,17 +9504,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.646</v>
+        <v>0.6009</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-182</v>
+        <v>-151</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9550,17 +9550,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9570,17 +9570,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5989</v>
+        <v>0.6228</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-149</v>
+        <v>-165</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6228</v>
+        <v>0.6227</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>-165</v>
@@ -9687,12 +9687,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9702,14 +9702,14 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6179</v>
+        <v>0.6038</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-162</v>
+        <v>-152</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>102</v>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9748,37 +9748,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Atlanta Braves</t>
+          <t>Chicago Sky @ Atlanta Dream</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago Sky +10.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.538</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-157</v>
+        <v>-116</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9819,32 +9819,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Kansas City Royals</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Indiana Fever +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5883</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9880,17 +9880,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Cleveland Guardians</t>
+          <t>Washington Mystics @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9900,17 +9900,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 149</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5534</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9946,17 +9946,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun @ Phoenix Mercury</t>
+          <t>Tampa Bay Rays @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9966,14 +9966,14 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5886</v>
+        <v>0.5694</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-143</v>
+        <v>-132</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>100</v>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -10017,12 +10017,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Minnesota Lynx</t>
+          <t>Minnesota Twins @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -10032,17 +10032,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5879</v>
+        <v>0.4945</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-143</v>
+        <v>102</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-102</v>
+        <v>130</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10078,37 +10078,37 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky @ Atlanta Dream</t>
+          <t>New York Liberty @ Indiana Fever</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago Sky +10.5</t>
+          <t>Indiana Fever</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.5381</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-118</v>
+        <v>-116</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-112</v>
+        <v>-107</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>117</v>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10215,12 +10215,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics @ Golden State Valkyries</t>
+          <t>San Diego Padres @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 148.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5705</v>
+        <v>0.5358999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-133</v>
+        <v>-115</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10276,17 +10276,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Chicago Cubs</t>
+          <t>Baltimore Orioles @ Houston Astros</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4945</v>
+        <v>0.5229</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>102</v>
+        <v>-110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10347,32 +10347,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Indiana Fever</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Indiana Fever</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5359</v>
+        <v>0.4104</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-115</v>
+        <v>144</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10413,12 +10413,12 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Boston Red Sox</t>
+          <t>Chicago White Sox @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -10432,10 +10432,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5488</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-130</v>
+        <v>-122</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>100</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11167,10 +11167,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6179</v>
+        <v>0.6227</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-162</v>
+        <v>-165</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>102</v>
@@ -11197,7 +11197,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3821</v>
+        <v>0.3773</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>128</v>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2959</v>
+        <v>0.2952</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>175</v>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 29.6% (fair +238). Your call.</t>
+          <t>Model 29.5% (fair +239). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11365,10 +11365,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.7048</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-238</v>
+        <v>-239</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 70.4% (fair -238). Your call.</t>
+          <t>Model 70.5% (fair -239). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11959,10 +11959,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4144</v>
+        <v>0.4229</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>103</v>
@@ -11989,7 +11989,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -12025,10 +12025,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4993</v>
+        <v>0.4904999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>117</v>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -12091,10 +12091,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4509</v>
+        <v>0.4547</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>125</v>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5490999999999999</v>
+        <v>0.5453</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12223,10 +12223,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5206</v>
+        <v>0.5159</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>102</v>
@@ -12253,7 +12253,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12289,10 +12289,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4794</v>
+        <v>0.4841</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-103</v>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12355,10 +12355,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4683</v>
+        <v>0.4512</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>122</v>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12421,10 +12421,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5317000000000001</v>
+        <v>0.5488</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-114</v>
+        <v>-122</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>100</v>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12487,10 +12487,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.5838</v>
+        <v>0.5896</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>-140</v>
+        <v>-144</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-163</v>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12553,10 +12553,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.4162</v>
+        <v>0.4104</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>170</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -13015,10 +13015,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.487</v>
+        <v>0.485</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>100</v>
@@ -13045,7 +13045,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -13081,10 +13081,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.513</v>
+        <v>0.515</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>100</v>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4803</v>
+        <v>0.4775</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>111</v>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13213,10 +13213,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4326</v>
+        <v>0.4353</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>113</v>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 43.3% (fair +131). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.6086</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-155</v>
+        <v>-157</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>-163</v>
@@ -13309,7 +13309,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -155). Your call.</t>
+          <t>Model 61.0% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13345,10 +13345,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.3914</v>
+        <v>0.3895999999999999</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>160</v>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +155). Your call.</t>
+          <t>Model 39.0% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4805</v>
+        <v>0.4859</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>-102</v>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5195</v>
+        <v>0.5141</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>104</v>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3398</v>
+        <v>0.3869</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>108</v>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5358999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-142</v>
+        <v>-115</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>108</v>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.6131</v>
+        <v>0.6081</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-158</v>
+        <v>-155</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>-150</v>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13741,10 +13741,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.3869</v>
+        <v>0.3919</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>147</v>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13807,7 +13807,7 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4716</v>
+        <v>0.4712</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>112</v>
@@ -13837,7 +13837,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13873,7 +13873,7 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5284</v>
+        <v>0.5288</v>
       </c>
       <c r="G54" s="14" t="n">
         <v>-112</v>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13939,10 +13939,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3945</v>
+        <v>0.4234</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>109</v>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -14005,10 +14005,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5200999999999999</v>
+        <v>0.4901</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>113</v>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3463</v>
+        <v>0.3558</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>178</v>
@@ -14101,7 +14101,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 34.6% (fair +189). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6442</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-189</v>
+        <v>-181</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>178</v>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14335,10 +14335,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4353</v>
+        <v>0.4306</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>122</v>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5647</v>
+        <v>0.5694</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-130</v>
+        <v>-132</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>100</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14467,10 +14467,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.3999</v>
+        <v>0.402</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H63" s="15" t="n">
         <v>170</v>
@@ -14497,7 +14497,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.6001000000000001</v>
+        <v>0.598</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-150</v>
+        <v>-149</v>
       </c>
       <c r="H64" s="15" t="n">
         <v>163</v>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4641999999999999</v>
+        <v>0.4658</v>
       </c>
       <c r="G65" s="14" t="n">
         <v>115</v>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5342</v>
       </c>
       <c r="G66" s="14" t="n">
         <v>-115</v>
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14731,10 +14731,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.3885</v>
+        <v>0.3962</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H67" s="15" t="n">
         <v>122</v>
@@ -14761,7 +14761,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 39.6% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.6114999999999999</v>
+        <v>0.6038</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-157</v>
+        <v>-152</v>
       </c>
       <c r="H68" s="15" t="n">
         <v>102</v>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 60.4% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14863,10 +14863,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.3779</v>
+        <v>0.3792</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>170</v>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14929,10 +14929,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.6221</v>
+        <v>0.6208</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-165</v>
+        <v>-164</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>167</v>
@@ -14959,7 +14959,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5168</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-108</v>
+        <v>-107</v>
       </c>
       <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
@@ -15023,7 +15023,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -15059,10 +15059,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4814</v>
+        <v>0.4833</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H72" s="15" t="n"/>
       <c r="I72" s="13">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.2853</v>
+        <v>0.2856</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>109</v>
@@ -15281,7 +15281,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 28.5% (fair +251). Your call.</t>
+          <t>Model 28.6% (fair +250). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15317,7 +15317,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6381</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="G76" s="14" t="n">
         <v>-176</v>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4281</v>
+        <v>0.425</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H77" s="15" t="n"/>
       <c r="I77" s="13">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15447,10 +15447,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5719</v>
+        <v>0.575</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-134</v>
+        <v>-135</v>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13">
@@ -15475,7 +15475,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15511,10 +15511,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5776</v>
+        <v>0.5646</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-137</v>
+        <v>-130</v>
       </c>
       <c r="H79" s="15" t="n"/>
       <c r="I79" s="13">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15575,10 +15575,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4224</v>
+        <v>0.4354</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H80" s="15" t="n"/>
       <c r="I80" s="13">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15639,10 +15639,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4807</v>
+        <v>0.4868</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H81" s="15" t="n"/>
       <c r="I81" s="13">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15703,10 +15703,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5193</v>
+        <v>0.5132</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H82" s="15" t="n"/>
       <c r="I82" s="13">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15899,10 +15899,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4845</v>
+        <v>0.4768</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>113</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15965,10 +15965,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5232</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-106</v>
+        <v>-110</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>105</v>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -106). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -16031,10 +16031,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.623</v>
+        <v>0.6189</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-165</v>
+        <v>-162</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>-163</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -16097,10 +16097,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.377</v>
+        <v>0.3811</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>178</v>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16163,10 +16163,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4778</v>
+        <v>0.4741</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>104</v>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16229,10 +16229,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5222</v>
+        <v>0.5259</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-104</v>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16295,10 +16295,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.386</v>
+        <v>0.3186</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>159</v>
+        <v>214</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>100</v>
@@ -16325,7 +16325,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 31.9% (fair +214). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16361,10 +16361,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.6009</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-112</v>
+        <v>-151</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>117</v>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16427,10 +16427,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3415</v>
+        <v>0.3641</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>156</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 34.2% (fair +193). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16493,10 +16493,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6585</v>
+        <v>0.6359</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-193</v>
+        <v>-175</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>167</v>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 65.8% (fair -193). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16559,10 +16559,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.474</v>
+        <v>0.4779</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>104</v>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16625,10 +16625,10 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.526</v>
+        <v>0.5221</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-111</v>
+        <v>-109</v>
       </c>
       <c r="H96" s="15" t="n">
         <v>-104</v>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.3204</v>
+        <v>0.3972</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="H97" s="15" t="n">
         <v>100</v>
@@ -16721,7 +16721,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 32.0% (fair +212). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16757,10 +16757,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5989</v>
+        <v>0.5172</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-149</v>
+        <v>-107</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>117</v>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16823,10 +16823,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.3634</v>
+        <v>0.3453</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>156</v>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 36.3% (fair +175). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16889,10 +16889,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6547000000000001</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-175</v>
+        <v>-190</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>167</v>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 63.7% (fair -175). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16961,7 +16961,7 @@
         <v>138</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4779</v>
+        <v>0.4934</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>113</v>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17153,10 +17153,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5221</v>
+        <v>0.5065999999999999</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-109</v>
+        <v>-103</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>105</v>
@@ -17183,7 +17183,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17219,10 +17219,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3943</v>
+        <v>0.3696</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>178</v>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 37.0% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17285,13 +17285,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6057</v>
+        <v>0.6304000000000001</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-154</v>
+        <v>-171</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>178</v>
+        <v>-186</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 60.6% (fair -154). Your call.</t>
+          <t>Model 63.0% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17351,13 +17351,13 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.5066999999999999</v>
+        <v>0.5085999999999999</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>-103</v>
+        <v>-104</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 50.7% (fair -103). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17417,10 +17417,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.4933</v>
+        <v>0.4914</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>117</v>
@@ -17447,7 +17447,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17483,10 +17483,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4358</v>
+        <v>0.4647</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>100</v>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17549,10 +17549,10 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.4774</v>
+        <v>0.4482</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H110" s="15" t="n">
         <v>115</v>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17615,13 +17615,13 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5935</v>
+        <v>0.5956</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-146</v>
+        <v>-147</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-143</v>
+        <v>-144</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.6% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17681,10 +17681,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4065</v>
+        <v>0.4044</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H112" s="15" t="n">
         <v>133</v>
@@ -17711,7 +17711,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 40.4% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17747,13 +17747,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4488576</v>
+        <v>0.4825</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17813,13 +17813,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5511424</v>
+        <v>0.5175</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-123</v>
+        <v>-107</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-102</v>
+        <v>104</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17875,17 +17875,17 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4851</v>
+        <v>0.4592</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17941,17 +17941,17 @@
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5149</v>
+        <v>0.4535999999999999</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-106</v>
+        <v>120</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-122</v>
+        <v>100</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -18011,13 +18011,13 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.6207</v>
+        <v>0.6042</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>-164</v>
+        <v>-153</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>-175</v>
+        <v>-155</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 60.4% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -18077,13 +18077,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.3793</v>
+        <v>0.3958</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 39.6% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18143,13 +18143,13 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5374</v>
       </c>
       <c r="G119" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>-113</v>
+        <v>-117</v>
       </c>
       <c r="I119" s="13">
         <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
@@ -18173,7 +18173,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -18209,13 +18209,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.4646</v>
+        <v>0.4626</v>
       </c>
       <c r="G120" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -18275,10 +18275,10 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.5516</v>
+        <v>0.5013</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>-123</v>
+        <v>-101</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>117</v>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 55.2% (fair -123). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -18341,13 +18341,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.4484</v>
+        <v>0.4987</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 44.8% (fair +123). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -18407,10 +18407,10 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5865</v>
+        <v>0.5835</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-142</v>
+        <v>-140</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>-156</v>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4135</v>
+        <v>0.4165</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H124" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I124" s="13">
         <f>IF($H$124="","",IF($H$124&lt;0,-$H$124/(-$H$124+100),100/($H$124+100)))</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -18539,10 +18539,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4822</v>
+        <v>0.478</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>108</v>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -18605,13 +18605,13 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5178</v>
+        <v>0.522</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H126" s="15" t="n">
-        <v>-111</v>
+        <v>-108</v>
       </c>
       <c r="I126" s="13">
         <f>IF($H$126="","",IF($H$126&lt;0,-$H$126/(-$H$126+100),100/($H$126+100)))</f>
@@ -18635,7 +18635,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -18671,7 +18671,7 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.5228</v>
+        <v>0.5229</v>
       </c>
       <c r="G127" s="14" t="n">
         <v>-110</v>
@@ -18737,7 +18737,7 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.4772</v>
+        <v>0.4771</v>
       </c>
       <c r="G128" s="14" t="n">
         <v>110</v>
@@ -18803,10 +18803,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.3249</v>
+        <v>0.3276</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>160</v>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 32.5% (fair +208). Your call.</t>
+          <t>Model 32.8% (fair +205). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18869,10 +18869,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.6751</v>
+        <v>0.6724</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>-208</v>
+        <v>-205</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>170</v>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 67.5% (fair -208). Your call.</t>
+          <t>Model 67.2% (fair -205). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.5032</v>
+        <v>0.5023</v>
       </c>
       <c r="G133" s="14" t="n">
         <v>-101</v>
@@ -19097,7 +19097,7 @@
       </c>
       <c r="N133" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O133" s="15" t="n"/>
@@ -19133,7 +19133,7 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.4968</v>
+        <v>0.4977</v>
       </c>
       <c r="G134" s="14" t="n">
         <v>101</v>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="N134" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O134" s="15" t="n"/>
@@ -19199,10 +19199,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.3915</v>
+        <v>0.3937</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>163</v>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +155). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -19265,10 +19265,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.6085</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-155</v>
+        <v>-154</v>
       </c>
       <c r="H136" s="15" t="n">
         <v>-170</v>
@@ -19295,7 +19295,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -155). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -19331,7 +19331,7 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.4495</v>
+        <v>0.4509</v>
       </c>
       <c r="G137" s="14" t="n">
         <v>122</v>
@@ -19361,7 +19361,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -19397,7 +19397,7 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.5505</v>
+        <v>0.5491</v>
       </c>
       <c r="G138" s="14" t="n">
         <v>-122</v>
@@ -19427,7 +19427,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.4961</v>
+        <v>0.4969</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H139" s="15" t="n">
         <v>108</v>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +102). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -19529,10 +19529,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.5039</v>
+        <v>0.5031</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>-102</v>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -19595,13 +19595,13 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.3618</v>
+        <v>0.3583</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="H141" s="15" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I141" s="13">
         <f>IF($H$141="","",IF($H$141&lt;0,-$H$141/(-$H$141+100),100/($H$141+100)))</f>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 36.2% (fair +176). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -19661,13 +19661,13 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.6382</v>
+        <v>0.6416999999999999</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-176</v>
+        <v>-179</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-182</v>
+        <v>-185</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -19691,7 +19691,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 63.8% (fair -176). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19859,13 +19859,13 @@
         </is>
       </c>
       <c r="F145" s="13" t="n">
-        <v>0.646</v>
+        <v>0.6341</v>
       </c>
       <c r="G145" s="14" t="n">
-        <v>-182</v>
+        <v>-173</v>
       </c>
       <c r="H145" s="15" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="I145" s="13">
         <f>IF($H$145="","",IF($H$145&lt;0,-$H$145/(-$H$145+100),100/($H$145+100)))</f>
@@ -19889,7 +19889,7 @@
       </c>
       <c r="N145" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -182). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O145" s="15" t="n"/>
@@ -19925,10 +19925,10 @@
         </is>
       </c>
       <c r="F146" s="13" t="n">
-        <v>0.354</v>
+        <v>0.3659</v>
       </c>
       <c r="G146" s="14" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H146" s="15" t="n">
         <v>100</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="N146" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +182). Your call.</t>
+          <t>Model 36.6% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O146" s="15" t="n"/>
@@ -19991,13 +19991,13 @@
         </is>
       </c>
       <c r="F147" s="13" t="n">
-        <v>0.4169</v>
+        <v>0.4181</v>
       </c>
       <c r="G147" s="14" t="n">
+        <v>139</v>
+      </c>
+      <c r="H147" s="15" t="n">
         <v>140</v>
-      </c>
-      <c r="H147" s="15" t="n">
-        <v>142</v>
       </c>
       <c r="I147" s="13">
         <f>IF($H$147="","",IF($H$147&lt;0,-$H$147/(-$H$147+100),100/($H$147+100)))</f>
@@ -20021,7 +20021,7 @@
       </c>
       <c r="N147" s="19" t="inlineStr">
         <is>
-          <t>Model 41.7% (fair +140). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O147" s="15" t="n"/>
@@ -20057,10 +20057,10 @@
         </is>
       </c>
       <c r="F148" s="13" t="n">
-        <v>0.5831</v>
+        <v>0.5819</v>
       </c>
       <c r="G148" s="14" t="n">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="H148" s="15" t="n">
         <v>-145</v>
@@ -20087,7 +20087,7 @@
       </c>
       <c r="N148" s="19" t="inlineStr">
         <is>
-          <t>Model 58.3% (fair -140). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O148" s="15" t="n"/>
@@ -20123,7 +20123,7 @@
         </is>
       </c>
       <c r="F149" s="13" t="n">
-        <v>0.4597</v>
+        <v>0.4594</v>
       </c>
       <c r="G149" s="14" t="n">
         <v>118</v>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="N149" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O149" s="15" t="n"/>
@@ -20187,7 +20187,7 @@
         </is>
       </c>
       <c r="F150" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.5406</v>
       </c>
       <c r="G150" s="14" t="n">
         <v>-118</v>
@@ -20215,7 +20215,7 @@
       </c>
       <c r="N150" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O150" s="15" t="n"/>
@@ -20251,10 +20251,10 @@
         </is>
       </c>
       <c r="F151" s="13" t="n">
-        <v>0.599</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="G151" s="14" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="H151" s="15" t="n"/>
       <c r="I151" s="13">
@@ -20279,7 +20279,7 @@
       </c>
       <c r="N151" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -149). Your call.</t>
+          <t>Model 59.9% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O151" s="15" t="n"/>
@@ -20315,10 +20315,10 @@
         </is>
       </c>
       <c r="F152" s="13" t="n">
-        <v>0.401</v>
+        <v>0.4007</v>
       </c>
       <c r="G152" s="14" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H152" s="15" t="n"/>
       <c r="I152" s="13">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="N152" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +149). Your call.</t>
+          <t>Model 40.1% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O152" s="15" t="n"/>
@@ -20379,10 +20379,10 @@
         </is>
       </c>
       <c r="F153" s="13" t="n">
-        <v>0.5976</v>
+        <v>0.5913</v>
       </c>
       <c r="G153" s="14" t="n">
-        <v>-149</v>
+        <v>-145</v>
       </c>
       <c r="H153" s="15" t="n"/>
       <c r="I153" s="13">
@@ -20407,7 +20407,7 @@
       </c>
       <c r="N153" s="19" t="inlineStr">
         <is>
-          <t>Model 59.8% (fair -149). Your call.</t>
+          <t>Model 59.1% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O153" s="15" t="n"/>
@@ -20443,10 +20443,10 @@
         </is>
       </c>
       <c r="F154" s="13" t="n">
-        <v>0.4024</v>
+        <v>0.4087</v>
       </c>
       <c r="G154" s="14" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H154" s="15" t="n"/>
       <c r="I154" s="13">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="N154" s="19" t="inlineStr">
         <is>
-          <t>Model 40.2% (fair +149). Your call.</t>
+          <t>Model 40.9% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O154" s="15" t="n"/>
@@ -20507,10 +20507,10 @@
         </is>
       </c>
       <c r="F155" s="13" t="n">
-        <v>0.4293</v>
+        <v>0.4244</v>
       </c>
       <c r="G155" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H155" s="15" t="n"/>
       <c r="I155" s="13">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="N155" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O155" s="15" t="n"/>
@@ -20571,10 +20571,10 @@
         </is>
       </c>
       <c r="F156" s="13" t="n">
-        <v>0.5707</v>
+        <v>0.5756</v>
       </c>
       <c r="G156" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H156" s="15" t="n"/>
       <c r="I156" s="13">
@@ -20599,7 +20599,7 @@
       </c>
       <c r="N156" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O156" s="15" t="n"/>
@@ -20635,10 +20635,10 @@
         </is>
       </c>
       <c r="F157" s="13" t="n">
-        <v>0.4753</v>
+        <v>0.4608</v>
       </c>
       <c r="G157" s="14" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="H157" s="15" t="n"/>
       <c r="I157" s="13">
@@ -20663,7 +20663,7 @@
       </c>
       <c r="N157" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +110). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O157" s="15" t="n"/>
@@ -20699,10 +20699,10 @@
         </is>
       </c>
       <c r="F158" s="13" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5392</v>
       </c>
       <c r="G158" s="14" t="n">
-        <v>-110</v>
+        <v>-117</v>
       </c>
       <c r="H158" s="15" t="n"/>
       <c r="I158" s="13">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="N158" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -110). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O158" s="15" t="n"/>
@@ -20904,13 +20904,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4641</v>
+        <v>0.4619</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -20970,13 +20970,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5359</v>
+        <v>0.5381</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -21000,7 +21000,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -21032,17 +21032,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 183.5</t>
+          <t>Over 184.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5202</v>
+        <v>0.5067</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-108</v>
+        <v>-103</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -21098,17 +21098,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 183.5</t>
+          <t>Under 184.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4798</v>
+        <v>0.4933</v>
       </c>
       <c r="G8" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H8" s="15" t="n">
         <v>108</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>107</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -21168,13 +21168,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6632173247506857</v>
+        <v>0.5883</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-197</v>
+        <v>-143</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 66.3% (fair -197). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -21234,10 +21234,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3367826752493143</v>
+        <v>0.4117</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>197</v>
+        <v>143</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>107</v>
@@ -21264,7 +21264,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 33.7% (fair +197). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -21306,7 +21306,7 @@
         <v>1157</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -21428,17 +21428,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 173.5</t>
+          <t>Over 175.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5879</v>
+        <v>0.6197049154642995</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-143</v>
+        <v>-163</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-102</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -21462,7 +21462,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -21494,17 +21494,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 173.5</t>
+          <t>Under 175.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4121</v>
+        <v>0.3802950845357005</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -21528,7 +21528,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -21560,17 +21560,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -14</t>
+          <t>Minnesota Lynx -13.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4411589559011642</v>
+        <v>0.4722</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -21626,11 +21626,11 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +14</t>
+          <t>Portland Fire +13.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5277410440988358</v>
+        <v>0.5278</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-112</v>
@@ -21702,7 +21702,7 @@
         <v>370</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -21824,17 +21824,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 148.5</t>
+          <t>Over 149</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5705</v>
+        <v>0.5534</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-133</v>
+        <v>-124</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -21890,17 +21890,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 148.5</t>
+          <t>Under 149</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4295</v>
+        <v>0.4244</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -22752,10 +22752,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4597</v>
+        <v>0.462</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>-108</v>
@@ -22782,7 +22782,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -22818,13 +22818,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5403</v>
+        <v>0.538</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-118</v>
+        <v>-116</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -22848,7 +22848,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -23016,10 +23016,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.5886</v>
+        <v>0.6698183982628872</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>-143</v>
+        <v>-203</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>100</v>
@@ -23046,7 +23046,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 67.0% (fair -203). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -23082,13 +23082,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.4114</v>
+        <v>0.3301816017371128</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 33.0% (fair +203). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -23144,17 +23144,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury -3.5</t>
+          <t>Phoenix Mercury -4.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4799</v>
+        <v>0.413058228452214</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -23178,7 +23178,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -23210,14 +23210,14 @@
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun +3.5</t>
+          <t>Connecticut Sun +4.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5201</v>
+        <v>0.586941771547786</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-108</v>
+        <v>-142</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>108</v>
@@ -23244,7 +23244,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -23359,28 +23359,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2493</v>
+        <v>0.2494</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.3941</v>
+        <v>0.3911</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-93.16</v>
+        <v>-99.11</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-13.7</v>
+        <v>-14.3</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5404</v>
+        <v>0.5382</v>
       </c>
     </row>
     <row r="6">
@@ -23390,28 +23390,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>0.2498</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.3888</v>
+        <v>0.3855</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-91.97</v>
+        <v>-97.92</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>-15.15</v>
+        <v>-15.79</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>5.59</v>
+        <v>5.5</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5577</v>
+        <v>0.5551</v>
       </c>
     </row>
     <row r="7">
@@ -23494,7 +23494,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=443, ECE 0.051 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=447, ECE 0.050 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -23589,16 +23589,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4593</v>
+        <v>0.4596</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4222</v>
+        <v>0.4234</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0371</v>
+        <v>-0.0362</v>
       </c>
     </row>
     <row r="21">
@@ -23608,16 +23608,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5429</v>
+        <v>0.5426</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5327</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="22">
